--- a/research/traditional_assets/database/data/italy/italy_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_drugs_biotechnology.xlsx
@@ -1528,7 +1528,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1665,22 +1665,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1292759721418993</v>
+        <v>0.1289999098087587</v>
       </c>
       <c r="C2">
-        <v>13.85507599292235</v>
+        <v>13.73491855018627</v>
       </c>
       <c r="D2">
-        <v>10.18507599292235</v>
+        <v>10.20359855018627</v>
       </c>
       <c r="E2">
-        <v>-0.368</v>
+        <v>-0.22932</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.13868</v>
       </c>
       <c r="G2">
         <v>3.67</v>
@@ -1701,28 +1701,28 @@
         <v>1.479</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.006975604</v>
       </c>
       <c r="N2">
-        <v>1.479</v>
+        <v>1.472024396</v>
       </c>
       <c r="O2">
-        <v>0.3549599999999999</v>
+        <v>0.35328585504</v>
       </c>
       <c r="P2">
-        <v>1.12404</v>
+        <v>1.11873854096</v>
       </c>
       <c r="Q2">
-        <v>1.58504</v>
+        <v>1.57973854096</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1292759721418993</v>
+        <v>0.1299167977866249</v>
       </c>
       <c r="T2">
-        <v>1.149078177305102</v>
+        <v>1.157899383514717</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>212.0246504818794</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1747,22 +1747,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1289999098087587</v>
+        <v>0.1287238474756181</v>
       </c>
       <c r="C3">
-        <v>13.73491855018627</v>
+        <v>13.61482860035815</v>
       </c>
       <c r="D3">
-        <v>10.20359855018627</v>
+        <v>10.22218860035815</v>
       </c>
       <c r="E3">
-        <v>-0.22932</v>
+        <v>-0.09064</v>
       </c>
       <c r="F3">
-        <v>0.13868</v>
+        <v>0.27736</v>
       </c>
       <c r="G3">
         <v>3.67</v>
@@ -1783,28 +1783,28 @@
         <v>1.479</v>
       </c>
       <c r="M3">
-        <v>0.006975604</v>
+        <v>0.013951208</v>
       </c>
       <c r="N3">
-        <v>1.472024396</v>
+        <v>1.465048792</v>
       </c>
       <c r="O3">
-        <v>0.35328585504</v>
+        <v>0.35161171008</v>
       </c>
       <c r="P3">
-        <v>1.11873854096</v>
+        <v>1.11343708192</v>
       </c>
       <c r="Q3">
-        <v>1.57973854096</v>
+        <v>1.57443708192</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1299167977866249</v>
+        <v>0.1305707015057328</v>
       </c>
       <c r="T3">
-        <v>1.157899383514717</v>
+        <v>1.166900614340855</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>212.0246504818794</v>
+        <v>106.0123252409397</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1829,22 +1829,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1287238474756181</v>
+        <v>0.1284477851424776</v>
       </c>
       <c r="C4">
-        <v>13.61482860035815</v>
+        <v>13.49480651300954</v>
       </c>
       <c r="D4">
-        <v>10.22218860035815</v>
+        <v>10.24084651300954</v>
       </c>
       <c r="E4">
-        <v>-0.09064</v>
+        <v>0.04804000000000003</v>
       </c>
       <c r="F4">
-        <v>0.27736</v>
+        <v>0.41604</v>
       </c>
       <c r="G4">
         <v>3.67</v>
@@ -1865,28 +1865,28 @@
         <v>1.479</v>
       </c>
       <c r="M4">
-        <v>0.013951208</v>
+        <v>0.020926812</v>
       </c>
       <c r="N4">
-        <v>1.465048792</v>
+        <v>1.458073188</v>
       </c>
       <c r="O4">
-        <v>0.35161171008</v>
+        <v>0.34993756512</v>
       </c>
       <c r="P4">
-        <v>1.11343708192</v>
+        <v>1.10813562288</v>
       </c>
       <c r="Q4">
-        <v>1.57443708192</v>
+        <v>1.56913562288</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1305707015057328</v>
+        <v>0.1312380877757501</v>
       </c>
       <c r="T4">
-        <v>1.166900614340855</v>
+        <v>1.17608743755516</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>106.0123252409397</v>
+        <v>70.67488349395981</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1911,22 +1911,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1284477851424776</v>
+        <v>0.128171722809337</v>
       </c>
       <c r="C5">
-        <v>13.49480651300954</v>
+        <v>13.3748526604152</v>
       </c>
       <c r="D5">
-        <v>10.24084651300954</v>
+        <v>10.25957266041519</v>
       </c>
       <c r="E5">
-        <v>0.04804000000000003</v>
+        <v>0.18672</v>
       </c>
       <c r="F5">
-        <v>0.41604</v>
+        <v>0.55472</v>
       </c>
       <c r="G5">
         <v>3.67</v>
@@ -1947,28 +1947,28 @@
         <v>1.479</v>
       </c>
       <c r="M5">
-        <v>0.020926812</v>
+        <v>0.027902416</v>
       </c>
       <c r="N5">
-        <v>1.458073188</v>
+        <v>1.451097584</v>
       </c>
       <c r="O5">
-        <v>0.34993756512</v>
+        <v>0.3482634201599999</v>
       </c>
       <c r="P5">
-        <v>1.10813562288</v>
+        <v>1.10283416384</v>
       </c>
       <c r="Q5">
-        <v>1.56913562288</v>
+        <v>1.56383416384</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1312380877757501</v>
+        <v>0.1319193779263927</v>
       </c>
       <c r="T5">
-        <v>1.17608743755516</v>
+        <v>1.185465652919764</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>70.67488349395981</v>
+        <v>53.00616262046985</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1993,22 +1993,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.128171722809337</v>
+        <v>0.1278956604761965</v>
       </c>
       <c r="C6">
-        <v>13.3748526604152</v>
+        <v>13.25496741757775</v>
       </c>
       <c r="D6">
-        <v>10.25957266041519</v>
+        <v>10.27836741757775</v>
       </c>
       <c r="E6">
-        <v>0.18672</v>
+        <v>0.3254</v>
       </c>
       <c r="F6">
-        <v>0.55472</v>
+        <v>0.6934</v>
       </c>
       <c r="G6">
         <v>3.67</v>
@@ -2029,28 +2029,28 @@
         <v>1.479</v>
       </c>
       <c r="M6">
-        <v>0.027902416</v>
+        <v>0.03487802</v>
       </c>
       <c r="N6">
-        <v>1.451097584</v>
+        <v>1.44412198</v>
       </c>
       <c r="O6">
-        <v>0.3482634201599999</v>
+        <v>0.3465892751999999</v>
       </c>
       <c r="P6">
-        <v>1.10283416384</v>
+        <v>1.0975327048</v>
       </c>
       <c r="Q6">
-        <v>1.56383416384</v>
+        <v>1.5585327048</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1319193779263927</v>
+        <v>0.1326150110275752</v>
       </c>
       <c r="T6">
-        <v>1.185465652919764</v>
+        <v>1.195041304397306</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>53.00616262046985</v>
+        <v>42.40493009637589</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2075,22 +2075,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1278956604761965</v>
+        <v>0.1276195981430559</v>
       </c>
       <c r="C7">
-        <v>13.25496741757775</v>
+        <v>13.13515116225281</v>
       </c>
       <c r="D7">
-        <v>10.27836741757775</v>
+        <v>10.2972311622528</v>
       </c>
       <c r="E7">
-        <v>0.3254</v>
+        <v>0.46408</v>
       </c>
       <c r="F7">
-        <v>0.6934</v>
+        <v>0.83208</v>
       </c>
       <c r="G7">
         <v>3.67</v>
@@ -2111,28 +2111,28 @@
         <v>1.479</v>
       </c>
       <c r="M7">
-        <v>0.03487802</v>
+        <v>0.041853624</v>
       </c>
       <c r="N7">
-        <v>1.44412198</v>
+        <v>1.437146376</v>
       </c>
       <c r="O7">
-        <v>0.3465892751999999</v>
+        <v>0.3449151302399999</v>
       </c>
       <c r="P7">
-        <v>1.0975327048</v>
+        <v>1.09223124576</v>
       </c>
       <c r="Q7">
-        <v>1.5585327048</v>
+        <v>1.55323124576</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1326150110275752</v>
+        <v>0.1333254448330382</v>
       </c>
       <c r="T7">
-        <v>1.195041304397306</v>
+        <v>1.204820693140328</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>42.40493009637589</v>
+        <v>35.3374417469799</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2157,22 +2157,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1276195981430559</v>
+        <v>0.1273435358099154</v>
       </c>
       <c r="C8">
-        <v>13.13515116225281</v>
+        <v>13.01540427497421</v>
       </c>
       <c r="D8">
-        <v>10.2972311622528</v>
+        <v>10.31616427497421</v>
       </c>
       <c r="E8">
-        <v>0.46408</v>
+        <v>0.60276</v>
       </c>
       <c r="F8">
-        <v>0.83208</v>
+        <v>0.97076</v>
       </c>
       <c r="G8">
         <v>3.67</v>
@@ -2193,28 +2193,28 @@
         <v>1.479</v>
       </c>
       <c r="M8">
-        <v>0.041853624</v>
+        <v>0.048829228</v>
       </c>
       <c r="N8">
-        <v>1.437146376</v>
+        <v>1.430170772</v>
       </c>
       <c r="O8">
-        <v>0.3449151302399999</v>
+        <v>0.34324098528</v>
       </c>
       <c r="P8">
-        <v>1.09223124576</v>
+        <v>1.08692978672</v>
       </c>
       <c r="Q8">
-        <v>1.55323124576</v>
+        <v>1.54792978672</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1333254448330382</v>
+        <v>0.1340511567848552</v>
       </c>
       <c r="T8">
-        <v>1.204820693140328</v>
+        <v>1.214810391318684</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>35.3374417469799</v>
+        <v>30.28923578312563</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2239,22 +2239,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1273435358099153</v>
+        <v>0.1270674734767748</v>
       </c>
       <c r="C9">
-        <v>13.01540427497421</v>
+        <v>12.89572713907967</v>
       </c>
       <c r="D9">
-        <v>10.31616427497421</v>
+        <v>10.33516713907967</v>
       </c>
       <c r="E9">
-        <v>0.6027600000000001</v>
+        <v>0.74144</v>
       </c>
       <c r="F9">
-        <v>0.9707600000000001</v>
+        <v>1.10944</v>
       </c>
       <c r="G9">
         <v>3.67</v>
@@ -2275,28 +2275,28 @@
         <v>1.479</v>
       </c>
       <c r="M9">
-        <v>0.048829228</v>
+        <v>0.055804832</v>
       </c>
       <c r="N9">
-        <v>1.430170772</v>
+        <v>1.423195168</v>
       </c>
       <c r="O9">
-        <v>0.34324098528</v>
+        <v>0.34156684032</v>
       </c>
       <c r="P9">
-        <v>1.08692978672</v>
+        <v>1.08162832768</v>
       </c>
       <c r="Q9">
-        <v>1.54792978672</v>
+        <v>1.54262832768</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1340511567848552</v>
+        <v>0.1347926450834508</v>
       </c>
       <c r="T9">
-        <v>1.214810391318684</v>
+        <v>1.225017256848744</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.28923578312563</v>
+        <v>26.50308131023493</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2321,22 +2321,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1270674734767748</v>
+        <v>0.1267914111436342</v>
       </c>
       <c r="C10">
-        <v>12.89572713907967</v>
+        <v>12.77612014073659</v>
       </c>
       <c r="D10">
-        <v>10.33516713907967</v>
+        <v>10.35424014073659</v>
       </c>
       <c r="E10">
-        <v>0.74144</v>
+        <v>0.8801199999999999</v>
       </c>
       <c r="F10">
-        <v>1.10944</v>
+        <v>1.24812</v>
       </c>
       <c r="G10">
         <v>3.67</v>
@@ -2357,28 +2357,28 @@
         <v>1.479</v>
       </c>
       <c r="M10">
-        <v>0.055804832</v>
+        <v>0.062780436</v>
       </c>
       <c r="N10">
-        <v>1.423195168</v>
+        <v>1.416219564</v>
       </c>
       <c r="O10">
-        <v>0.34156684032</v>
+        <v>0.33989269536</v>
       </c>
       <c r="P10">
-        <v>1.08162832768</v>
+        <v>1.07632686864</v>
       </c>
       <c r="Q10">
-        <v>1.54262832768</v>
+        <v>1.53732686864</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1347926450834508</v>
+        <v>0.1355504298281695</v>
       </c>
       <c r="T10">
-        <v>1.225017256848744</v>
+        <v>1.235448449093749</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.50308131023493</v>
+        <v>23.5582944979866</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2403,22 +2403,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1267914111436342</v>
+        <v>0.1265153488104937</v>
       </c>
       <c r="C11">
-        <v>12.77612014073659</v>
+        <v>12.65658366896827</v>
       </c>
       <c r="D11">
-        <v>10.35424014073659</v>
+        <v>10.37338366896827</v>
       </c>
       <c r="E11">
-        <v>0.8801199999999999</v>
+        <v>1.0188</v>
       </c>
       <c r="F11">
-        <v>1.24812</v>
+        <v>1.3868</v>
       </c>
       <c r="G11">
         <v>3.67</v>
@@ -2439,28 +2439,28 @@
         <v>1.479</v>
       </c>
       <c r="M11">
-        <v>0.062780436</v>
+        <v>0.06975603999999999</v>
       </c>
       <c r="N11">
-        <v>1.416219564</v>
+        <v>1.40924396</v>
       </c>
       <c r="O11">
-        <v>0.33989269536</v>
+        <v>0.3382185504</v>
       </c>
       <c r="P11">
-        <v>1.07632686864</v>
+        <v>1.0710254096</v>
       </c>
       <c r="Q11">
-        <v>1.53732686864</v>
+        <v>1.5320254096</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1355504298281695</v>
+        <v>0.1363250542338819</v>
       </c>
       <c r="T11">
-        <v>1.235448449093749</v>
+        <v>1.246111445610866</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.5582944979866</v>
+        <v>21.20246504818794</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2485,22 +2485,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1265153488104937</v>
+        <v>0.1262392864773531</v>
       </c>
       <c r="C12">
-        <v>12.65658366896827</v>
+        <v>12.53711811568034</v>
       </c>
       <c r="D12">
-        <v>10.37338366896827</v>
+        <v>10.39259811568034</v>
       </c>
       <c r="E12">
-        <v>1.0188</v>
+        <v>1.15748</v>
       </c>
       <c r="F12">
-        <v>1.3868</v>
+        <v>1.52548</v>
       </c>
       <c r="G12">
         <v>3.67</v>
@@ -2521,28 +2521,28 @@
         <v>1.479</v>
       </c>
       <c r="M12">
-        <v>0.06975603999999999</v>
+        <v>0.07673164399999999</v>
       </c>
       <c r="N12">
-        <v>1.40924396</v>
+        <v>1.402268356</v>
       </c>
       <c r="O12">
-        <v>0.3382185504</v>
+        <v>0.33654440544</v>
       </c>
       <c r="P12">
-        <v>1.0710254096</v>
+        <v>1.06572395056</v>
       </c>
       <c r="Q12">
-        <v>1.5320254096</v>
+        <v>1.52672395056</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1363250542338819</v>
+        <v>0.1371170859296102</v>
       </c>
       <c r="T12">
-        <v>1.246111445610866</v>
+        <v>1.257014060027245</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.20246504818794</v>
+        <v>19.2749682256254</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2567,22 +2567,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1262392864773531</v>
+        <v>0.1259632241442125</v>
       </c>
       <c r="C13">
-        <v>12.53711811568034</v>
+        <v>12.41772387568746</v>
       </c>
       <c r="D13">
-        <v>10.39259811568034</v>
+        <v>10.41188387568746</v>
       </c>
       <c r="E13">
-        <v>1.15748</v>
+        <v>1.29616</v>
       </c>
       <c r="F13">
-        <v>1.52548</v>
+        <v>1.66416</v>
       </c>
       <c r="G13">
         <v>3.67</v>
@@ -2603,28 +2603,28 @@
         <v>1.479</v>
       </c>
       <c r="M13">
-        <v>0.07673164399999999</v>
+        <v>0.083707248</v>
       </c>
       <c r="N13">
-        <v>1.402268356</v>
+        <v>1.395292752</v>
       </c>
       <c r="O13">
-        <v>0.33654440544</v>
+        <v>0.33487026048</v>
       </c>
       <c r="P13">
-        <v>1.06572395056</v>
+        <v>1.06042249152</v>
       </c>
       <c r="Q13">
-        <v>1.52672395056</v>
+        <v>1.52142249152</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1371170859296102</v>
+        <v>0.1379271183456961</v>
       </c>
       <c r="T13">
-        <v>1.257014060027245</v>
+        <v>1.268164461134904</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.2749682256254</v>
+        <v>17.66872087348995</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2649,22 +2649,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1259632241442125</v>
+        <v>0.125687161811072</v>
       </c>
       <c r="C14">
-        <v>12.41772387568746</v>
+        <v>12.29840134674045</v>
       </c>
       <c r="D14">
-        <v>10.41188387568746</v>
+        <v>10.43124134674045</v>
       </c>
       <c r="E14">
-        <v>1.29616</v>
+        <v>1.43484</v>
       </c>
       <c r="F14">
-        <v>1.66416</v>
+        <v>1.80284</v>
       </c>
       <c r="G14">
         <v>3.67</v>
@@ -2685,28 +2685,28 @@
         <v>1.479</v>
       </c>
       <c r="M14">
-        <v>0.083707248</v>
+        <v>0.09068285199999999</v>
       </c>
       <c r="N14">
-        <v>1.395292752</v>
+        <v>1.388317148</v>
       </c>
       <c r="O14">
-        <v>0.33487026048</v>
+        <v>0.3331961155199999</v>
       </c>
       <c r="P14">
-        <v>1.06042249152</v>
+        <v>1.05512103248</v>
       </c>
       <c r="Q14">
-        <v>1.52142249152</v>
+        <v>1.51612103248</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1379271183456961</v>
+        <v>0.1387557721966345</v>
       </c>
       <c r="T14">
-        <v>1.268164461134904</v>
+        <v>1.279571193302509</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.66872087348995</v>
+        <v>16.30958849860611</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.125687161811072</v>
+        <v>0.1254110994779314</v>
       </c>
       <c r="C15">
-        <v>12.29840134674045</v>
+        <v>12.17915092955356</v>
       </c>
       <c r="D15">
-        <v>10.43124134674045</v>
+        <v>10.45067092955357</v>
       </c>
       <c r="E15">
-        <v>1.43484</v>
+        <v>1.57352</v>
       </c>
       <c r="F15">
-        <v>1.80284</v>
+        <v>1.94152</v>
       </c>
       <c r="G15">
         <v>3.67</v>
@@ -2767,28 +2767,28 @@
         <v>1.479</v>
       </c>
       <c r="M15">
-        <v>0.09068285199999999</v>
+        <v>0.097658456</v>
       </c>
       <c r="N15">
-        <v>1.388317148</v>
+        <v>1.381341544</v>
       </c>
       <c r="O15">
-        <v>0.3331961155199999</v>
+        <v>0.3315219705599999</v>
       </c>
       <c r="P15">
-        <v>1.05512103248</v>
+        <v>1.04981957344</v>
       </c>
       <c r="Q15">
-        <v>1.51612103248</v>
+        <v>1.51081957344</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1387557721966345</v>
+        <v>0.1396036970673621</v>
       </c>
       <c r="T15">
-        <v>1.279571193302509</v>
+        <v>1.291243198311222</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.30958849860611</v>
+        <v>15.14461789156281</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2813,22 +2813,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1254110994779314</v>
+        <v>0.1251350371447909</v>
       </c>
       <c r="C16">
-        <v>12.17915092955356</v>
+        <v>12.05997302783216</v>
       </c>
       <c r="D16">
-        <v>10.45067092955357</v>
+        <v>10.47017302783216</v>
       </c>
       <c r="E16">
-        <v>1.57352</v>
+        <v>1.712200000000001</v>
       </c>
       <c r="F16">
-        <v>1.94152</v>
+        <v>2.0802</v>
       </c>
       <c r="G16">
         <v>3.67</v>
@@ -2849,28 +2849,28 @@
         <v>1.479</v>
       </c>
       <c r="M16">
-        <v>0.097658456</v>
+        <v>0.10463406</v>
       </c>
       <c r="N16">
-        <v>1.381341544</v>
+        <v>1.37436594</v>
       </c>
       <c r="O16">
-        <v>0.3315219705599999</v>
+        <v>0.3298478256</v>
       </c>
       <c r="P16">
-        <v>1.04981957344</v>
+        <v>1.0445181144</v>
       </c>
       <c r="Q16">
-        <v>1.51081957344</v>
+        <v>1.5055181144</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1396036970673621</v>
+        <v>0.1404715731115187</v>
       </c>
       <c r="T16">
-        <v>1.291243198311222</v>
+        <v>1.303189838731904</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.14461789156281</v>
+        <v>14.13497669879196</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2895,22 +2895,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1251350371447909</v>
+        <v>0.1248589748116503</v>
       </c>
       <c r="C17">
-        <v>12.05997302783216</v>
+        <v>11.94086804830067</v>
       </c>
       <c r="D17">
-        <v>10.47017302783216</v>
+        <v>10.48974804830067</v>
       </c>
       <c r="E17">
-        <v>1.7122</v>
+        <v>1.85088</v>
       </c>
       <c r="F17">
-        <v>2.0802</v>
+        <v>2.21888</v>
       </c>
       <c r="G17">
         <v>3.67</v>
@@ -2931,28 +2931,28 @@
         <v>1.479</v>
       </c>
       <c r="M17">
-        <v>0.10463406</v>
+        <v>0.111609664</v>
       </c>
       <c r="N17">
-        <v>1.37436594</v>
+        <v>1.367390336</v>
       </c>
       <c r="O17">
-        <v>0.3298478256</v>
+        <v>0.32817368064</v>
       </c>
       <c r="P17">
-        <v>1.0445181144</v>
+        <v>1.03921665536</v>
       </c>
       <c r="Q17">
-        <v>1.5055181144</v>
+        <v>1.50021665536</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1404715731115187</v>
+        <v>0.1413601128710123</v>
       </c>
       <c r="T17">
-        <v>1.303189838731904</v>
+        <v>1.315420922972127</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.13497669879196</v>
+        <v>13.25154065511746</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2977,22 +2977,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1248589748116503</v>
+        <v>0.1247767124785097</v>
       </c>
       <c r="C18">
-        <v>11.94086804830067</v>
+        <v>11.80803526662429</v>
       </c>
       <c r="D18">
-        <v>10.48974804830067</v>
+        <v>10.49559526662429</v>
       </c>
       <c r="E18">
-        <v>1.85088</v>
+        <v>1.98956</v>
       </c>
       <c r="F18">
-        <v>2.21888</v>
+        <v>2.35756</v>
       </c>
       <c r="G18">
         <v>3.67</v>
@@ -3013,45 +3013,45 @@
         <v>1.479</v>
       </c>
       <c r="M18">
-        <v>0.111609664</v>
+        <v>0.122121608</v>
       </c>
       <c r="N18">
-        <v>1.367390336</v>
+        <v>1.356878392</v>
       </c>
       <c r="O18">
-        <v>0.32817368064</v>
+        <v>0.32565081408</v>
       </c>
       <c r="P18">
-        <v>1.03921665536</v>
+        <v>1.03122757792</v>
       </c>
       <c r="Q18">
-        <v>1.50021665536</v>
+        <v>1.49222757792</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1413601128710123</v>
+        <v>0.1422700632271202</v>
       </c>
       <c r="T18">
-        <v>1.315420922972127</v>
+        <v>1.3279467321338</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.24</v>
       </c>
       <c r="W18">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.25154065511746</v>
+        <v>12.1108788544612</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3059,22 +3059,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1247767124785097</v>
+        <v>0.1245120501453692</v>
       </c>
       <c r="C19">
-        <v>11.80803526662429</v>
+        <v>11.68821180639104</v>
       </c>
       <c r="D19">
-        <v>10.49559526662429</v>
+        <v>10.51445180639104</v>
       </c>
       <c r="E19">
-        <v>1.98956</v>
+        <v>2.12824</v>
       </c>
       <c r="F19">
-        <v>2.35756</v>
+        <v>2.49624</v>
       </c>
       <c r="G19">
         <v>3.67</v>
@@ -3095,28 +3095,28 @@
         <v>1.479</v>
       </c>
       <c r="M19">
-        <v>0.122121608</v>
+        <v>0.129305232</v>
       </c>
       <c r="N19">
-        <v>1.356878392</v>
+        <v>1.349694768</v>
       </c>
       <c r="O19">
-        <v>0.32565081408</v>
+        <v>0.32392674432</v>
       </c>
       <c r="P19">
-        <v>1.03122757792</v>
+        <v>1.02576802368</v>
       </c>
       <c r="Q19">
-        <v>1.49222757792</v>
+        <v>1.48676802368</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1422700632271202</v>
+        <v>0.1432022074943527</v>
       </c>
       <c r="T19">
-        <v>1.3279467321338</v>
+        <v>1.340778048836002</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.1108788544612</v>
+        <v>11.43805225143558</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3141,22 +3141,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1245120501453692</v>
+        <v>0.1242473878122287</v>
       </c>
       <c r="C20">
-        <v>11.68821180639104</v>
+        <v>11.56845622397764</v>
       </c>
       <c r="D20">
-        <v>10.51445180639104</v>
+        <v>10.53337622397764</v>
       </c>
       <c r="E20">
-        <v>2.12824</v>
+        <v>2.26692</v>
       </c>
       <c r="F20">
-        <v>2.49624</v>
+        <v>2.63492</v>
       </c>
       <c r="G20">
         <v>3.67</v>
@@ -3177,28 +3177,28 @@
         <v>1.479</v>
       </c>
       <c r="M20">
-        <v>0.129305232</v>
+        <v>0.136488856</v>
       </c>
       <c r="N20">
-        <v>1.349694768</v>
+        <v>1.342511144</v>
       </c>
       <c r="O20">
-        <v>0.32392674432</v>
+        <v>0.32220267456</v>
       </c>
       <c r="P20">
-        <v>1.02576802368</v>
+        <v>1.02030846944</v>
       </c>
       <c r="Q20">
-        <v>1.48676802368</v>
+        <v>1.48130846944</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1432022074943527</v>
+        <v>0.1441573676694181</v>
       </c>
       <c r="T20">
-        <v>1.340778048836002</v>
+        <v>1.353926188172827</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.43805225143558</v>
+        <v>10.83604950136002</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3223,22 +3223,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1242473878122287</v>
+        <v>0.1239827254790881</v>
       </c>
       <c r="C21">
-        <v>11.56845622397764</v>
+        <v>11.44876888655427</v>
       </c>
       <c r="D21">
-        <v>10.53337622397764</v>
+        <v>10.55236888655427</v>
       </c>
       <c r="E21">
-        <v>2.26692</v>
+        <v>2.4056</v>
       </c>
       <c r="F21">
-        <v>2.63492</v>
+        <v>2.7736</v>
       </c>
       <c r="G21">
         <v>3.67</v>
@@ -3259,28 +3259,28 @@
         <v>1.479</v>
       </c>
       <c r="M21">
-        <v>0.136488856</v>
+        <v>0.14367248</v>
       </c>
       <c r="N21">
-        <v>1.342511144</v>
+        <v>1.33532752</v>
       </c>
       <c r="O21">
-        <v>0.32220267456</v>
+        <v>0.3204786048</v>
       </c>
       <c r="P21">
-        <v>1.02030846944</v>
+        <v>1.0148489152</v>
       </c>
       <c r="Q21">
-        <v>1.48130846944</v>
+        <v>1.4758489152</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1441573676694181</v>
+        <v>0.1451364068488601</v>
       </c>
       <c r="T21">
-        <v>1.353926188172827</v>
+        <v>1.367403030993072</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.83604950136002</v>
+        <v>10.29424702629202</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3305,22 +3305,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1239827254790881</v>
+        <v>0.1239893831459475</v>
       </c>
       <c r="C22">
-        <v>11.44876888655427</v>
+        <v>11.30961028021551</v>
       </c>
       <c r="D22">
-        <v>10.55236888655427</v>
+        <v>10.55189028021551</v>
       </c>
       <c r="E22">
-        <v>2.4056</v>
+        <v>2.544280000000001</v>
       </c>
       <c r="F22">
-        <v>2.7736</v>
+        <v>2.91228</v>
       </c>
       <c r="G22">
         <v>3.67</v>
@@ -3341,45 +3341,45 @@
         <v>1.479</v>
       </c>
       <c r="M22">
-        <v>0.14367248</v>
+        <v>0.15580698</v>
       </c>
       <c r="N22">
-        <v>1.33532752</v>
+        <v>1.32319302</v>
       </c>
       <c r="O22">
-        <v>0.3204786048</v>
+        <v>0.3175663248</v>
       </c>
       <c r="P22">
-        <v>1.0148489152</v>
+        <v>1.0056266952</v>
       </c>
       <c r="Q22">
-        <v>1.4758489152</v>
+        <v>1.4666266952</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1451364068488601</v>
+        <v>0.1461402318303133</v>
       </c>
       <c r="T22">
-        <v>1.367403030993072</v>
+        <v>1.3812210597075</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.24</v>
       </c>
       <c r="W22">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.29424702629202</v>
+        <v>9.492514391845601</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3387,22 +3387,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1239893831459475</v>
+        <v>0.123737640812807</v>
       </c>
       <c r="C23">
-        <v>11.30961028021551</v>
+        <v>11.18905780022504</v>
       </c>
       <c r="D23">
-        <v>10.55189028021551</v>
+        <v>10.57001780022504</v>
       </c>
       <c r="E23">
-        <v>2.54428</v>
+        <v>2.68296</v>
       </c>
       <c r="F23">
-        <v>2.91228</v>
+        <v>3.05096</v>
       </c>
       <c r="G23">
         <v>3.67</v>
@@ -3423,28 +3423,28 @@
         <v>1.479</v>
       </c>
       <c r="M23">
-        <v>0.15580698</v>
+        <v>0.16322636</v>
       </c>
       <c r="N23">
-        <v>1.32319302</v>
+        <v>1.31577364</v>
       </c>
       <c r="O23">
-        <v>0.3175663248</v>
+        <v>0.3157856736</v>
       </c>
       <c r="P23">
-        <v>1.0056266952</v>
+        <v>0.9999879664</v>
       </c>
       <c r="Q23">
-        <v>1.4666266952</v>
+        <v>1.4609879664</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1461402318303133</v>
+        <v>0.1471697959138551</v>
       </c>
       <c r="T23">
-        <v>1.3812210597075</v>
+        <v>1.395393396850504</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.492514391845603</v>
+        <v>9.06103646494353</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3469,22 +3469,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.123737640812807</v>
+        <v>0.1234858984796664</v>
       </c>
       <c r="C24">
-        <v>11.18905780022504</v>
+        <v>11.06856771142168</v>
       </c>
       <c r="D24">
-        <v>10.57001780022504</v>
+        <v>10.58820771142168</v>
       </c>
       <c r="E24">
-        <v>2.68296</v>
+        <v>2.82164</v>
       </c>
       <c r="F24">
-        <v>3.05096</v>
+        <v>3.18964</v>
       </c>
       <c r="G24">
         <v>3.67</v>
@@ -3505,28 +3505,28 @@
         <v>1.479</v>
       </c>
       <c r="M24">
-        <v>0.16322636</v>
+        <v>0.17064574</v>
       </c>
       <c r="N24">
-        <v>1.31577364</v>
+        <v>1.30835426</v>
       </c>
       <c r="O24">
-        <v>0.3157856736</v>
+        <v>0.3140050223999999</v>
       </c>
       <c r="P24">
-        <v>0.9999879664</v>
+        <v>0.9943492375999998</v>
       </c>
       <c r="Q24">
-        <v>1.4609879664</v>
+        <v>1.4553492376</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1471697959138551</v>
+        <v>0.1482261019216447</v>
       </c>
       <c r="T24">
-        <v>1.395393396850504</v>
+        <v>1.409933846646572</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.06103646494353</v>
+        <v>8.66707835777207</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3551,22 +3551,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1234858984796664</v>
+        <v>0.1232341561465258</v>
       </c>
       <c r="C25">
-        <v>11.06856771142168</v>
+        <v>10.94814033646712</v>
       </c>
       <c r="D25">
-        <v>10.58820771142168</v>
+        <v>10.60646033646712</v>
       </c>
       <c r="E25">
-        <v>2.82164</v>
+        <v>2.96032</v>
       </c>
       <c r="F25">
-        <v>3.18964</v>
+        <v>3.32832</v>
       </c>
       <c r="G25">
         <v>3.67</v>
@@ -3587,28 +3587,28 @@
         <v>1.479</v>
       </c>
       <c r="M25">
-        <v>0.17064574</v>
+        <v>0.17806512</v>
       </c>
       <c r="N25">
-        <v>1.30835426</v>
+        <v>1.30093488</v>
       </c>
       <c r="O25">
-        <v>0.3140050223999999</v>
+        <v>0.3122243712</v>
       </c>
       <c r="P25">
-        <v>0.9943492375999998</v>
+        <v>0.9887105087999999</v>
       </c>
       <c r="Q25">
-        <v>1.4553492376</v>
+        <v>1.4497105088</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1482261019216447</v>
+        <v>0.1493102054559551</v>
       </c>
       <c r="T25">
-        <v>1.409933846646572</v>
+        <v>1.424856939858327</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.66707835777207</v>
+        <v>8.305950092864901</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3633,22 +3633,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1232341561465258</v>
+        <v>0.1229824138133853</v>
       </c>
       <c r="C26">
-        <v>10.94814033646712</v>
+        <v>10.82777600025175</v>
       </c>
       <c r="D26">
-        <v>10.60646033646712</v>
+        <v>10.62477600025175</v>
       </c>
       <c r="E26">
-        <v>2.96032</v>
+        <v>3.099</v>
       </c>
       <c r="F26">
-        <v>3.32832</v>
+        <v>3.467</v>
       </c>
       <c r="G26">
         <v>3.67</v>
@@ -3669,28 +3669,28 @@
         <v>1.479</v>
       </c>
       <c r="M26">
-        <v>0.17806512</v>
+        <v>0.1854845</v>
       </c>
       <c r="N26">
-        <v>1.30093488</v>
+        <v>1.2935155</v>
       </c>
       <c r="O26">
-        <v>0.3122243712</v>
+        <v>0.3104437199999999</v>
       </c>
       <c r="P26">
-        <v>0.9887105087999999</v>
+        <v>0.98307178</v>
       </c>
       <c r="Q26">
-        <v>1.4497105088</v>
+        <v>1.44407178</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1493102054559551</v>
+        <v>0.1504232184178471</v>
       </c>
       <c r="T26">
-        <v>1.424856939858327</v>
+        <v>1.440177982222395</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.305950092864901</v>
+        <v>7.973712089150306</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3715,22 +3715,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1229824138133853</v>
+        <v>0.1227306714802447</v>
       </c>
       <c r="C27">
-        <v>10.82777600025175</v>
+        <v>10.70747502991403</v>
       </c>
       <c r="D27">
-        <v>10.62477600025175</v>
+        <v>10.64315502991403</v>
       </c>
       <c r="E27">
-        <v>3.099</v>
+        <v>3.23768</v>
       </c>
       <c r="F27">
-        <v>3.467</v>
+        <v>3.60568</v>
       </c>
       <c r="G27">
         <v>3.67</v>
@@ -3751,28 +3751,28 @@
         <v>1.479</v>
       </c>
       <c r="M27">
-        <v>0.1854845</v>
+        <v>0.19290388</v>
       </c>
       <c r="N27">
-        <v>1.2935155</v>
+        <v>1.28609612</v>
       </c>
       <c r="O27">
-        <v>0.3104437199999999</v>
+        <v>0.3086630687999999</v>
       </c>
       <c r="P27">
-        <v>0.98307178</v>
+        <v>0.9774330511999999</v>
       </c>
       <c r="Q27">
-        <v>1.44407178</v>
+        <v>1.4384330512</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1504232184178471</v>
+        <v>0.1515663128111415</v>
       </c>
       <c r="T27">
-        <v>1.440177982222395</v>
+        <v>1.455913106812519</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.973712089150306</v>
+        <v>7.667030854952217</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1227306714802447</v>
+        <v>0.1226430891471042</v>
       </c>
       <c r="C28">
-        <v>10.70747502991403</v>
+        <v>10.57520409799991</v>
       </c>
       <c r="D28">
-        <v>10.64315502991403</v>
+        <v>10.64956409799991</v>
       </c>
       <c r="E28">
-        <v>3.23768</v>
+        <v>3.37636</v>
       </c>
       <c r="F28">
-        <v>3.60568</v>
+        <v>3.74436</v>
       </c>
       <c r="G28">
         <v>3.67</v>
@@ -3833,45 +3833,45 @@
         <v>1.479</v>
       </c>
       <c r="M28">
-        <v>0.19290388</v>
+        <v>0.203318748</v>
       </c>
       <c r="N28">
-        <v>1.28609612</v>
+        <v>1.275681252</v>
       </c>
       <c r="O28">
-        <v>0.3086630687999999</v>
+        <v>0.30616350048</v>
       </c>
       <c r="P28">
-        <v>0.9774330511999999</v>
+        <v>0.9695177515199999</v>
       </c>
       <c r="Q28">
-        <v>1.4384330512</v>
+        <v>1.43051775152</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1515663128111415</v>
+        <v>0.1527407248590468</v>
       </c>
       <c r="T28">
-        <v>1.455913106812519</v>
+        <v>1.472079330706481</v>
       </c>
       <c r="U28">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.24</v>
       </c>
       <c r="W28">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.667030854952217</v>
+        <v>7.274292285136439</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3879,22 +3879,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1226430891471042</v>
+        <v>0.1223974268139636</v>
       </c>
       <c r="C29">
-        <v>10.57520409799991</v>
+        <v>10.45454234611243</v>
       </c>
       <c r="D29">
-        <v>10.64956409799991</v>
+        <v>10.66758234611243</v>
       </c>
       <c r="E29">
-        <v>3.37636</v>
+        <v>3.51504</v>
       </c>
       <c r="F29">
-        <v>3.74436</v>
+        <v>3.88304</v>
       </c>
       <c r="G29">
         <v>3.67</v>
@@ -3915,28 +3915,28 @@
         <v>1.479</v>
       </c>
       <c r="M29">
-        <v>0.203318748</v>
+        <v>0.210849072</v>
       </c>
       <c r="N29">
-        <v>1.275681252</v>
+        <v>1.268150928</v>
       </c>
       <c r="O29">
-        <v>0.30616350048</v>
+        <v>0.30435622272</v>
       </c>
       <c r="P29">
-        <v>0.9695177515199999</v>
+        <v>0.9637947052799999</v>
       </c>
       <c r="Q29">
-        <v>1.43051775152</v>
+        <v>1.42479470528</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1527407248590468</v>
+        <v>0.1539477594638383</v>
       </c>
       <c r="T29">
-        <v>1.472079330706481</v>
+        <v>1.488694616375277</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.274292285136439</v>
+        <v>7.014496132095851</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3961,22 +3961,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1223974268139636</v>
+        <v>0.1221517644808231</v>
       </c>
       <c r="C30">
-        <v>10.45454234611243</v>
+        <v>10.33394166855405</v>
       </c>
       <c r="D30">
-        <v>10.66758234611243</v>
+        <v>10.68566166855405</v>
       </c>
       <c r="E30">
-        <v>3.51504</v>
+        <v>3.65372</v>
       </c>
       <c r="F30">
-        <v>3.88304</v>
+        <v>4.02172</v>
       </c>
       <c r="G30">
         <v>3.67</v>
@@ -3997,28 +3997,28 @@
         <v>1.479</v>
       </c>
       <c r="M30">
-        <v>0.210849072</v>
+        <v>0.218379396</v>
       </c>
       <c r="N30">
-        <v>1.268150928</v>
+        <v>1.260620604</v>
       </c>
       <c r="O30">
-        <v>0.30435622272</v>
+        <v>0.30254894496</v>
       </c>
       <c r="P30">
-        <v>0.9637947052799999</v>
+        <v>0.9580716590399999</v>
       </c>
       <c r="Q30">
-        <v>1.42479470528</v>
+        <v>1.41907165904</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1539477594638383</v>
+        <v>0.1551887950434128</v>
       </c>
       <c r="T30">
-        <v>1.488694616375277</v>
+        <v>1.505777938260095</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.014496132095851</v>
+        <v>6.77261695512703</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4043,22 +4043,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1221517644808231</v>
+        <v>0.1219061021476825</v>
       </c>
       <c r="C31">
-        <v>10.33394166855405</v>
+        <v>10.21340237637661</v>
       </c>
       <c r="D31">
-        <v>10.68566166855405</v>
+        <v>10.70380237637661</v>
       </c>
       <c r="E31">
-        <v>3.65372</v>
+        <v>3.7924</v>
       </c>
       <c r="F31">
-        <v>4.02172</v>
+        <v>4.1604</v>
       </c>
       <c r="G31">
         <v>3.67</v>
@@ -4079,28 +4079,28 @@
         <v>1.479</v>
       </c>
       <c r="M31">
-        <v>0.218379396</v>
+        <v>0.22590972</v>
       </c>
       <c r="N31">
-        <v>1.260620604</v>
+        <v>1.25309028</v>
       </c>
       <c r="O31">
-        <v>0.30254894496</v>
+        <v>0.3007416672</v>
       </c>
       <c r="P31">
-        <v>0.9580716590399999</v>
+        <v>0.9523486127999999</v>
       </c>
       <c r="Q31">
-        <v>1.41907165904</v>
+        <v>1.4133486128</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1551887950434128</v>
+        <v>0.1564652887824036</v>
       </c>
       <c r="T31">
-        <v>1.505777938260095</v>
+        <v>1.523349355055907</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.77261695512703</v>
+        <v>6.546863056622795</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4125,22 +4125,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1219061021476825</v>
+        <v>0.1216604398145419</v>
       </c>
       <c r="C32">
-        <v>10.21340237637661</v>
+        <v>10.09292478274779</v>
       </c>
       <c r="D32">
-        <v>10.70380237637661</v>
+        <v>10.72200478274779</v>
       </c>
       <c r="E32">
-        <v>3.7924</v>
+        <v>3.93108</v>
       </c>
       <c r="F32">
-        <v>4.1604</v>
+        <v>4.29908</v>
       </c>
       <c r="G32">
         <v>3.67</v>
@@ -4161,28 +4161,28 @@
         <v>1.479</v>
       </c>
       <c r="M32">
-        <v>0.22590972</v>
+        <v>0.233440044</v>
       </c>
       <c r="N32">
-        <v>1.25309028</v>
+        <v>1.245559956</v>
       </c>
       <c r="O32">
-        <v>0.3007416672</v>
+        <v>0.2989343894399999</v>
       </c>
       <c r="P32">
-        <v>0.9523486127999999</v>
+        <v>0.94662556656</v>
       </c>
       <c r="Q32">
-        <v>1.4133486128</v>
+        <v>1.40762556656</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1564652887824036</v>
+        <v>0.1577787823399159</v>
       </c>
       <c r="T32">
-        <v>1.523349355055907</v>
+        <v>1.541430088280583</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.546863056622795</v>
+        <v>6.335673925763995</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4207,22 +4207,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1216604398145419</v>
+        <v>0.1214147774814014</v>
       </c>
       <c r="C33">
-        <v>10.09292478274779</v>
+        <v>9.972509202969125</v>
       </c>
       <c r="D33">
-        <v>10.72200478274779</v>
+        <v>10.74026920296912</v>
       </c>
       <c r="E33">
-        <v>3.93108</v>
+        <v>4.06976</v>
       </c>
       <c r="F33">
-        <v>4.29908</v>
+        <v>4.43776</v>
       </c>
       <c r="G33">
         <v>3.67</v>
@@ -4243,28 +4243,28 @@
         <v>1.479</v>
       </c>
       <c r="M33">
-        <v>0.233440044</v>
+        <v>0.240970368</v>
       </c>
       <c r="N33">
-        <v>1.245559956</v>
+        <v>1.238029632</v>
       </c>
       <c r="O33">
-        <v>0.2989343894399999</v>
+        <v>0.29712711168</v>
       </c>
       <c r="P33">
-        <v>0.94662556656</v>
+        <v>0.9409025203199999</v>
       </c>
       <c r="Q33">
-        <v>1.40762556656</v>
+        <v>1.40190252032</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1577787823399159</v>
+        <v>0.1591309080608844</v>
       </c>
       <c r="T33">
-        <v>1.541430088280583</v>
+        <v>1.560042607776574</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.335673925763995</v>
+        <v>6.137684115583872</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4289,22 +4289,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1214147774814014</v>
+        <v>0.1214199151482608</v>
       </c>
       <c r="C34">
-        <v>9.972509202969125</v>
+        <v>9.833446592404695</v>
       </c>
       <c r="D34">
-        <v>10.74026920296912</v>
+        <v>10.7398865924047</v>
       </c>
       <c r="E34">
-        <v>4.06976</v>
+        <v>4.20844</v>
       </c>
       <c r="F34">
-        <v>4.43776</v>
+        <v>4.576440000000001</v>
       </c>
       <c r="G34">
         <v>3.67</v>
@@ -4325,45 +4325,45 @@
         <v>1.479</v>
       </c>
       <c r="M34">
-        <v>0.240970368</v>
+        <v>0.253077132</v>
       </c>
       <c r="N34">
-        <v>1.238029632</v>
+        <v>1.225922868</v>
       </c>
       <c r="O34">
-        <v>0.29712711168</v>
+        <v>0.2942214883199999</v>
       </c>
       <c r="P34">
-        <v>0.9409025203199999</v>
+        <v>0.9317013796799999</v>
       </c>
       <c r="Q34">
-        <v>1.40190252032</v>
+        <v>1.39270137968</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1591309080608844</v>
+        <v>0.1605233957436729</v>
       </c>
       <c r="T34">
-        <v>1.560042607776574</v>
+        <v>1.57921072486946</v>
       </c>
       <c r="U34">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.24</v>
       </c>
       <c r="W34">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>6.137684115583872</v>
+        <v>5.844068123863517</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4371,22 +4371,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1214199151482608</v>
+        <v>0.1211818528151203</v>
       </c>
       <c r="C35">
-        <v>9.833446592404695</v>
+        <v>9.712524169587097</v>
       </c>
       <c r="D35">
-        <v>10.7398865924047</v>
+        <v>10.7576441695871</v>
       </c>
       <c r="E35">
-        <v>4.20844</v>
+        <v>4.34712</v>
       </c>
       <c r="F35">
-        <v>4.576440000000001</v>
+        <v>4.715120000000001</v>
       </c>
       <c r="G35">
         <v>3.67</v>
@@ -4407,28 +4407,28 @@
         <v>1.479</v>
       </c>
       <c r="M35">
-        <v>0.253077132</v>
+        <v>0.260746136</v>
       </c>
       <c r="N35">
-        <v>1.225922868</v>
+        <v>1.218253864</v>
       </c>
       <c r="O35">
-        <v>0.2942214883199999</v>
+        <v>0.2923809273599999</v>
       </c>
       <c r="P35">
-        <v>0.9317013796799999</v>
+        <v>0.9258729366399998</v>
       </c>
       <c r="Q35">
-        <v>1.39270137968</v>
+        <v>1.38687293664</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1605233957436729</v>
+        <v>0.1619580800229095</v>
       </c>
       <c r="T35">
-        <v>1.57921072486946</v>
+        <v>1.598959693995464</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.844068123863517</v>
+        <v>5.672183767279297</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4453,22 +4453,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1211818528151203</v>
+        <v>0.1209437904819797</v>
       </c>
       <c r="C36">
-        <v>9.712524169587097</v>
+        <v>9.59166056560052</v>
       </c>
       <c r="D36">
-        <v>10.7576441695871</v>
+        <v>10.77546056560052</v>
       </c>
       <c r="E36">
-        <v>4.34712</v>
+        <v>4.4858</v>
       </c>
       <c r="F36">
-        <v>4.715120000000001</v>
+        <v>4.853800000000001</v>
       </c>
       <c r="G36">
         <v>3.67</v>
@@ -4489,28 +4489,28 @@
         <v>1.479</v>
       </c>
       <c r="M36">
-        <v>0.260746136</v>
+        <v>0.2684151400000001</v>
       </c>
       <c r="N36">
-        <v>1.218253864</v>
+        <v>1.21058486</v>
       </c>
       <c r="O36">
-        <v>0.2923809273599999</v>
+        <v>0.2905403663999999</v>
       </c>
       <c r="P36">
-        <v>0.9258729366399998</v>
+        <v>0.9200444935999998</v>
       </c>
       <c r="Q36">
-        <v>1.38687293664</v>
+        <v>1.3810444936</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1619580800229095</v>
+        <v>0.1634369084338149</v>
       </c>
       <c r="T36">
-        <v>1.598959693995464</v>
+        <v>1.619316323709959</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.672183767279297</v>
+        <v>5.510121373928459</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4535,22 +4535,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1209437904819797</v>
+        <v>0.1207057281488391</v>
       </c>
       <c r="C37">
-        <v>9.59166056560052</v>
+        <v>9.47085607317022</v>
       </c>
       <c r="D37">
-        <v>10.77546056560052</v>
+        <v>10.79333607317022</v>
       </c>
       <c r="E37">
-        <v>4.4858</v>
+        <v>4.62448</v>
       </c>
       <c r="F37">
-        <v>4.853800000000001</v>
+        <v>4.99248</v>
       </c>
       <c r="G37">
         <v>3.67</v>
@@ -4571,28 +4571,28 @@
         <v>1.479</v>
       </c>
       <c r="M37">
-        <v>0.2684151400000001</v>
+        <v>0.276084144</v>
       </c>
       <c r="N37">
-        <v>1.21058486</v>
+        <v>1.202915856</v>
       </c>
       <c r="O37">
-        <v>0.2905403663999999</v>
+        <v>0.2886998054399999</v>
       </c>
       <c r="P37">
-        <v>0.9200444935999998</v>
+        <v>0.9142160505599999</v>
       </c>
       <c r="Q37">
-        <v>1.3810444936</v>
+        <v>1.37521605056</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1634369084338149</v>
+        <v>0.1649619502325612</v>
       </c>
       <c r="T37">
-        <v>1.619316323709959</v>
+        <v>1.640309098103034</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.510121373928459</v>
+        <v>5.35706244687489</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4617,22 +4617,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1207057281488391</v>
+        <v>0.1204676658156986</v>
       </c>
       <c r="C38">
-        <v>9.470856073170221</v>
+        <v>9.350110986967088</v>
       </c>
       <c r="D38">
-        <v>10.79333607317022</v>
+        <v>10.81127098696709</v>
       </c>
       <c r="E38">
-        <v>4.624479999999999</v>
+        <v>4.76316</v>
       </c>
       <c r="F38">
-        <v>4.99248</v>
+        <v>5.13116</v>
       </c>
       <c r="G38">
         <v>3.67</v>
@@ -4653,28 +4653,28 @@
         <v>1.479</v>
       </c>
       <c r="M38">
-        <v>0.276084144</v>
+        <v>0.283753148</v>
       </c>
       <c r="N38">
-        <v>1.202915856</v>
+        <v>1.195246852</v>
       </c>
       <c r="O38">
-        <v>0.28869980544</v>
+        <v>0.2868592444799999</v>
       </c>
       <c r="P38">
-        <v>0.91421605056</v>
+        <v>0.9083876075199999</v>
       </c>
       <c r="Q38">
-        <v>1.37521605056</v>
+        <v>1.36938760752</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1649619502325612</v>
+        <v>0.1665354060566644</v>
       </c>
       <c r="T38">
-        <v>1.640309098103033</v>
+        <v>1.661968309778427</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.357062446874892</v>
+        <v>5.212276975337732</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4699,22 +4699,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1204676658156986</v>
+        <v>0.120229603482558</v>
       </c>
       <c r="C39">
-        <v>9.350110986967088</v>
+        <v>9.229425603623858</v>
       </c>
       <c r="D39">
-        <v>10.81127098696709</v>
+        <v>10.82926560362386</v>
       </c>
       <c r="E39">
-        <v>4.76316</v>
+        <v>4.90184</v>
       </c>
       <c r="F39">
-        <v>5.13116</v>
+        <v>5.26984</v>
       </c>
       <c r="G39">
         <v>3.67</v>
@@ -4735,28 +4735,28 @@
         <v>1.479</v>
       </c>
       <c r="M39">
-        <v>0.283753148</v>
+        <v>0.291422152</v>
       </c>
       <c r="N39">
-        <v>1.195246852</v>
+        <v>1.187577848</v>
       </c>
       <c r="O39">
-        <v>0.2868592444799999</v>
+        <v>0.28501868352</v>
       </c>
       <c r="P39">
-        <v>0.9083876075199999</v>
+        <v>0.90255916448</v>
       </c>
       <c r="Q39">
-        <v>1.36938760752</v>
+        <v>1.36355916448</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1665354060566644</v>
+        <v>0.1681596185202549</v>
       </c>
       <c r="T39">
-        <v>1.661968309778427</v>
+        <v>1.684326205701414</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.212276975337732</v>
+        <v>5.075111791776212</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4781,22 +4781,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.120229603482558</v>
+        <v>0.1199915411494175</v>
       </c>
       <c r="C40">
-        <v>9.229425603623858</v>
+        <v>9.108800221751455</v>
       </c>
       <c r="D40">
-        <v>10.82926560362386</v>
+        <v>10.84732022175146</v>
       </c>
       <c r="E40">
-        <v>4.90184</v>
+        <v>5.04052</v>
       </c>
       <c r="F40">
-        <v>5.26984</v>
+        <v>5.40852</v>
       </c>
       <c r="G40">
         <v>3.67</v>
@@ -4817,28 +4817,28 @@
         <v>1.479</v>
       </c>
       <c r="M40">
-        <v>0.291422152</v>
+        <v>0.299091156</v>
       </c>
       <c r="N40">
-        <v>1.187577848</v>
+        <v>1.179908844</v>
       </c>
       <c r="O40">
-        <v>0.28501868352</v>
+        <v>0.28317812256</v>
       </c>
       <c r="P40">
-        <v>0.90255916448</v>
+        <v>0.8967307214399999</v>
       </c>
       <c r="Q40">
-        <v>1.36355916448</v>
+        <v>1.35773072144</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1681596185202549</v>
+        <v>0.1698370838515041</v>
       </c>
       <c r="T40">
-        <v>1.684326205701414</v>
+        <v>1.707417147392368</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.075111791776212</v>
+        <v>4.944980720192207</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1199915411494175</v>
+        <v>0.1197534788162769</v>
       </c>
       <c r="C41">
-        <v>9.108800221751455</v>
+        <v>8.988235141955508</v>
       </c>
       <c r="D41">
-        <v>10.84732022175146</v>
+        <v>10.86543514195551</v>
       </c>
       <c r="E41">
-        <v>5.04052</v>
+        <v>5.1792</v>
       </c>
       <c r="F41">
-        <v>5.40852</v>
+        <v>5.5472</v>
       </c>
       <c r="G41">
         <v>3.67</v>
@@ -4899,28 +4899,28 @@
         <v>1.479</v>
       </c>
       <c r="M41">
-        <v>0.299091156</v>
+        <v>0.30676016</v>
       </c>
       <c r="N41">
-        <v>1.179908844</v>
+        <v>1.17223984</v>
       </c>
       <c r="O41">
-        <v>0.28317812256</v>
+        <v>0.2813375616</v>
       </c>
       <c r="P41">
-        <v>0.8967307214399999</v>
+        <v>0.8909022783999998</v>
       </c>
       <c r="Q41">
-        <v>1.35773072144</v>
+        <v>1.3519022784</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1698370838515041</v>
+        <v>0.1715704646937949</v>
       </c>
       <c r="T41">
-        <v>1.707417147392368</v>
+        <v>1.731277787139687</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.944980720192207</v>
+        <v>4.821356202187403</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4945,22 +4945,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1197534788162769</v>
+        <v>0.1195154164831364</v>
       </c>
       <c r="C42">
-        <v>8.988235141955508</v>
+        <v>8.867730666853049</v>
       </c>
       <c r="D42">
-        <v>10.86543514195551</v>
+        <v>10.88361066685305</v>
       </c>
       <c r="E42">
-        <v>5.1792</v>
+        <v>5.317880000000001</v>
       </c>
       <c r="F42">
-        <v>5.5472</v>
+        <v>5.685880000000001</v>
       </c>
       <c r="G42">
         <v>3.67</v>
@@ -4981,28 +4981,28 @@
         <v>1.479</v>
       </c>
       <c r="M42">
-        <v>0.30676016</v>
+        <v>0.314429164</v>
       </c>
       <c r="N42">
-        <v>1.17223984</v>
+        <v>1.164570836</v>
       </c>
       <c r="O42">
-        <v>0.2813375616</v>
+        <v>0.2794970006399999</v>
       </c>
       <c r="P42">
-        <v>0.8909022783999998</v>
+        <v>0.8850738353599998</v>
       </c>
       <c r="Q42">
-        <v>1.3519022784</v>
+        <v>1.34607383536</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1715704646937949</v>
+        <v>0.1733626042087057</v>
       </c>
       <c r="T42">
-        <v>1.731277787139687</v>
+        <v>1.755947262132678</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.821356202187403</v>
+        <v>4.703762148475514</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5027,22 +5027,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1195154164831364</v>
+        <v>0.1192773541499958</v>
       </c>
       <c r="C43">
-        <v>8.867730666853049</v>
+        <v>8.747287101089348</v>
       </c>
       <c r="D43">
-        <v>10.88361066685305</v>
+        <v>10.90184710108935</v>
       </c>
       <c r="E43">
-        <v>5.317880000000001</v>
+        <v>5.456560000000001</v>
       </c>
       <c r="F43">
-        <v>5.685880000000001</v>
+        <v>5.824560000000001</v>
       </c>
       <c r="G43">
         <v>3.67</v>
@@ -5063,28 +5063,28 @@
         <v>1.479</v>
       </c>
       <c r="M43">
-        <v>0.314429164</v>
+        <v>0.3220981680000001</v>
       </c>
       <c r="N43">
-        <v>1.164570836</v>
+        <v>1.156901832</v>
       </c>
       <c r="O43">
-        <v>0.2794970006399999</v>
+        <v>0.2776564396799999</v>
       </c>
       <c r="P43">
-        <v>0.8850738353599998</v>
+        <v>0.8792453923199999</v>
       </c>
       <c r="Q43">
-        <v>1.34607383536</v>
+        <v>1.34024539232</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1733626042087057</v>
+        <v>0.1752165416379238</v>
       </c>
       <c r="T43">
-        <v>1.755947262132678</v>
+        <v>1.781467408677152</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.703762148475514</v>
+        <v>4.591767811607049</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5109,22 +5109,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1192773541499958</v>
+        <v>0.1198562918168553</v>
       </c>
       <c r="C44">
-        <v>8.747287101089347</v>
+        <v>8.564364356509415</v>
       </c>
       <c r="D44">
-        <v>10.90184710108935</v>
+        <v>10.85760435650941</v>
       </c>
       <c r="E44">
-        <v>5.45656</v>
+        <v>5.59524</v>
       </c>
       <c r="F44">
-        <v>5.82456</v>
+        <v>5.96324</v>
       </c>
       <c r="G44">
         <v>3.67</v>
@@ -5145,45 +5145,45 @@
         <v>1.479</v>
       </c>
       <c r="M44">
-        <v>0.322098168</v>
+        <v>0.344675272</v>
       </c>
       <c r="N44">
-        <v>1.156901832</v>
+        <v>1.134324728</v>
       </c>
       <c r="O44">
-        <v>0.27765643968</v>
+        <v>0.2722379347199999</v>
       </c>
       <c r="P44">
-        <v>0.87924539232</v>
+        <v>0.8620867932799998</v>
       </c>
       <c r="Q44">
-        <v>1.34024539232</v>
+        <v>1.32308679328</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1752165416379238</v>
+        <v>0.1771355295032548</v>
       </c>
       <c r="T44">
-        <v>1.781467408677152</v>
+        <v>1.807882998960027</v>
       </c>
       <c r="U44">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V44">
         <v>0.24</v>
       </c>
       <c r="W44">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.59176781160705</v>
+        <v>4.290995380718811</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5191,22 +5191,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1198562918168553</v>
+        <v>0.1196372294837147</v>
       </c>
       <c r="C45">
-        <v>8.564364356509415</v>
+        <v>8.442382927337524</v>
       </c>
       <c r="D45">
-        <v>10.85760435650941</v>
+        <v>10.87430292733752</v>
       </c>
       <c r="E45">
-        <v>5.59524</v>
+        <v>5.733919999999999</v>
       </c>
       <c r="F45">
-        <v>5.96324</v>
+        <v>6.10192</v>
       </c>
       <c r="G45">
         <v>3.67</v>
@@ -5227,28 +5227,28 @@
         <v>1.479</v>
       </c>
       <c r="M45">
-        <v>0.344675272</v>
+        <v>0.352690976</v>
       </c>
       <c r="N45">
-        <v>1.134324728</v>
+        <v>1.126309024</v>
       </c>
       <c r="O45">
-        <v>0.2722379347199999</v>
+        <v>0.2703141657599999</v>
       </c>
       <c r="P45">
-        <v>0.8620867932799998</v>
+        <v>0.8559948582399999</v>
       </c>
       <c r="Q45">
-        <v>1.32308679328</v>
+        <v>1.31699485824</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1771355295032548</v>
+        <v>0.1791230526494905</v>
       </c>
       <c r="T45">
-        <v>1.807882998960027</v>
+        <v>1.835242003181577</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.290995380718811</v>
+        <v>4.193472758429747</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5273,22 +5273,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1196372294837147</v>
+        <v>0.1194181671505741</v>
       </c>
       <c r="C46">
-        <v>8.442382927337524</v>
+        <v>8.320452940779973</v>
       </c>
       <c r="D46">
-        <v>10.87430292733752</v>
+        <v>10.89105294077997</v>
       </c>
       <c r="E46">
-        <v>5.733919999999999</v>
+        <v>5.8726</v>
       </c>
       <c r="F46">
-        <v>6.10192</v>
+        <v>6.240600000000001</v>
       </c>
       <c r="G46">
         <v>3.67</v>
@@ -5309,28 +5309,28 @@
         <v>1.479</v>
       </c>
       <c r="M46">
-        <v>0.352690976</v>
+        <v>0.3607066800000001</v>
       </c>
       <c r="N46">
-        <v>1.126309024</v>
+        <v>1.11829332</v>
       </c>
       <c r="O46">
-        <v>0.2703141657599999</v>
+        <v>0.2683903967999999</v>
       </c>
       <c r="P46">
-        <v>0.8559948582399999</v>
+        <v>0.8499029231999999</v>
       </c>
       <c r="Q46">
-        <v>1.31699485824</v>
+        <v>1.3109029232</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1791230526494905</v>
+        <v>0.1811828493646802</v>
       </c>
       <c r="T46">
-        <v>1.835242003181577</v>
+        <v>1.863595880283911</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.193472758429747</v>
+        <v>4.100284474909086</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5355,22 +5355,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1194181671505741</v>
+        <v>0.1191991048174336</v>
       </c>
       <c r="C47">
-        <v>8.320452940779973</v>
+        <v>8.198574634919265</v>
       </c>
       <c r="D47">
-        <v>10.89105294077997</v>
+        <v>10.90785463491927</v>
       </c>
       <c r="E47">
-        <v>5.8726</v>
+        <v>6.01128</v>
       </c>
       <c r="F47">
-        <v>6.240600000000001</v>
+        <v>6.379280000000001</v>
       </c>
       <c r="G47">
         <v>3.67</v>
@@ -5391,28 +5391,28 @@
         <v>1.479</v>
       </c>
       <c r="M47">
-        <v>0.3607066800000001</v>
+        <v>0.3687223840000001</v>
       </c>
       <c r="N47">
-        <v>1.11829332</v>
+        <v>1.110277616</v>
       </c>
       <c r="O47">
-        <v>0.2683903967999999</v>
+        <v>0.26646662784</v>
       </c>
       <c r="P47">
-        <v>0.8499029231999999</v>
+        <v>0.8438109881599999</v>
       </c>
       <c r="Q47">
-        <v>1.3109029232</v>
+        <v>1.30481098816</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1811828493646802</v>
+        <v>0.1833189348470992</v>
       </c>
       <c r="T47">
-        <v>1.863595880283911</v>
+        <v>1.892999900982628</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.100284474909086</v>
+        <v>4.011147855889323</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5437,22 +5437,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1191991048174336</v>
+        <v>0.120230242484293</v>
       </c>
       <c r="C48">
-        <v>8.198574634919265</v>
+        <v>7.981257222688203</v>
       </c>
       <c r="D48">
-        <v>10.90785463491927</v>
+        <v>10.8292172226882</v>
       </c>
       <c r="E48">
-        <v>6.01128</v>
+        <v>6.14996</v>
       </c>
       <c r="F48">
-        <v>6.379280000000001</v>
+        <v>6.51796</v>
       </c>
       <c r="G48">
         <v>3.67</v>
@@ -5473,45 +5473,45 @@
         <v>1.479</v>
       </c>
       <c r="M48">
-        <v>0.3687223840000001</v>
+        <v>0.399550948</v>
       </c>
       <c r="N48">
-        <v>1.110277616</v>
+        <v>1.079449052</v>
       </c>
       <c r="O48">
-        <v>0.26646662784</v>
+        <v>0.2590677724799999</v>
       </c>
       <c r="P48">
-        <v>0.8438109881599999</v>
+        <v>0.8203812795199998</v>
       </c>
       <c r="Q48">
-        <v>1.30481098816</v>
+        <v>1.28138127952</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1833189348470992</v>
+        <v>0.1855356273288548</v>
       </c>
       <c r="T48">
-        <v>1.892999900982628</v>
+        <v>1.923513507368088</v>
       </c>
       <c r="U48">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V48">
         <v>0.24</v>
       </c>
       <c r="W48">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.011147855889323</v>
+        <v>3.701655589614568</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5519,22 +5519,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.120230242484293</v>
+        <v>0.1200377801511525</v>
       </c>
       <c r="C49">
-        <v>7.981257222688203</v>
+        <v>7.857168752135673</v>
       </c>
       <c r="D49">
-        <v>10.8292172226882</v>
+        <v>10.84380875213567</v>
       </c>
       <c r="E49">
-        <v>6.14996</v>
+        <v>6.28864</v>
       </c>
       <c r="F49">
-        <v>6.51796</v>
+        <v>6.65664</v>
       </c>
       <c r="G49">
         <v>3.67</v>
@@ -5555,28 +5555,28 @@
         <v>1.479</v>
       </c>
       <c r="M49">
-        <v>0.399550948</v>
+        <v>0.408052032</v>
       </c>
       <c r="N49">
-        <v>1.079449052</v>
+        <v>1.070947968</v>
       </c>
       <c r="O49">
-        <v>0.2590677724799999</v>
+        <v>0.2570275123199999</v>
       </c>
       <c r="P49">
-        <v>0.8203812795199998</v>
+        <v>0.8139204556799999</v>
       </c>
       <c r="Q49">
-        <v>1.28138127952</v>
+        <v>1.27492045568</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1855356273288548</v>
+        <v>0.1878375772137547</v>
       </c>
       <c r="T49">
-        <v>1.923513507368088</v>
+        <v>1.955200713999143</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.701655589614568</v>
+        <v>3.624537764830932</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5601,22 +5601,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1200377801511525</v>
+        <v>0.1198453178180119</v>
       </c>
       <c r="C50">
-        <v>7.857168752135673</v>
+        <v>7.733119656543995</v>
       </c>
       <c r="D50">
-        <v>10.84380875213567</v>
+        <v>10.85843965654399</v>
       </c>
       <c r="E50">
-        <v>6.28864</v>
+        <v>6.42732</v>
       </c>
       <c r="F50">
-        <v>6.65664</v>
+        <v>6.79532</v>
       </c>
       <c r="G50">
         <v>3.67</v>
@@ -5637,28 +5637,28 @@
         <v>1.479</v>
       </c>
       <c r="M50">
-        <v>0.408052032</v>
+        <v>0.416553116</v>
       </c>
       <c r="N50">
-        <v>1.070947968</v>
+        <v>1.062446884</v>
       </c>
       <c r="O50">
-        <v>0.2570275123199999</v>
+        <v>0.25498725216</v>
       </c>
       <c r="P50">
-        <v>0.8139204556799999</v>
+        <v>0.8074596318399999</v>
       </c>
       <c r="Q50">
-        <v>1.27492045568</v>
+        <v>1.26845963184</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1878375772137547</v>
+        <v>0.1902297996431606</v>
       </c>
       <c r="T50">
-        <v>1.955200713999143</v>
+        <v>1.988130556184357</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.624537764830932</v>
+        <v>3.550567606364994</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5683,22 +5683,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1198453178180119</v>
+        <v>0.1207168554848713</v>
       </c>
       <c r="C51">
-        <v>7.733119656543995</v>
+        <v>7.528499228056787</v>
       </c>
       <c r="D51">
-        <v>10.85843965654399</v>
+        <v>10.79249922805679</v>
       </c>
       <c r="E51">
-        <v>6.42732</v>
+        <v>6.566</v>
       </c>
       <c r="F51">
-        <v>6.79532</v>
+        <v>6.934</v>
       </c>
       <c r="G51">
         <v>3.67</v>
@@ -5719,45 +5719,45 @@
         <v>1.479</v>
       </c>
       <c r="M51">
-        <v>0.416553116</v>
+        <v>0.4444694</v>
       </c>
       <c r="N51">
-        <v>1.062446884</v>
+        <v>1.0345306</v>
       </c>
       <c r="O51">
-        <v>0.25498725216</v>
+        <v>0.248287344</v>
       </c>
       <c r="P51">
-        <v>0.8074596318399999</v>
+        <v>0.7862432559999999</v>
       </c>
       <c r="Q51">
-        <v>1.26845963184</v>
+        <v>1.247243256</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1902297996431606</v>
+        <v>0.1927177109697427</v>
       </c>
       <c r="T51">
-        <v>1.988130556184357</v>
+        <v>2.02237759205698</v>
       </c>
       <c r="U51">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V51">
         <v>0.24</v>
       </c>
       <c r="W51">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.550567606364994</v>
+        <v>3.327563157328715</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5765,22 +5765,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1207168554848713</v>
+        <v>0.1205456731517308</v>
       </c>
       <c r="C52">
-        <v>7.528499228056787</v>
+        <v>7.402707582521334</v>
       </c>
       <c r="D52">
-        <v>10.79249922805679</v>
+        <v>10.80538758252133</v>
       </c>
       <c r="E52">
-        <v>6.566</v>
+        <v>6.70468</v>
       </c>
       <c r="F52">
-        <v>6.934</v>
+        <v>7.07268</v>
       </c>
       <c r="G52">
         <v>3.67</v>
@@ -5801,28 +5801,28 @@
         <v>1.479</v>
       </c>
       <c r="M52">
-        <v>0.4444694</v>
+        <v>0.453358788</v>
       </c>
       <c r="N52">
-        <v>1.0345306</v>
+        <v>1.025641212</v>
       </c>
       <c r="O52">
-        <v>0.248287344</v>
+        <v>0.2461538908799999</v>
       </c>
       <c r="P52">
-        <v>0.7862432559999999</v>
+        <v>0.7794873211199999</v>
       </c>
       <c r="Q52">
-        <v>1.247243256</v>
+        <v>1.24048732112</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1927177109697427</v>
+        <v>0.1953071696974098</v>
       </c>
       <c r="T52">
-        <v>2.02237759205698</v>
+        <v>2.058022466128485</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.327563157328715</v>
+        <v>3.262316820910506</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5847,22 +5847,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1205456731517308</v>
+        <v>0.1203744908185902</v>
       </c>
       <c r="C53">
-        <v>7.402707582521334</v>
+        <v>7.276946756220963</v>
       </c>
       <c r="D53">
-        <v>10.80538758252133</v>
+        <v>10.81830675622096</v>
       </c>
       <c r="E53">
-        <v>6.70468</v>
+        <v>6.84336</v>
       </c>
       <c r="F53">
-        <v>7.07268</v>
+        <v>7.21136</v>
       </c>
       <c r="G53">
         <v>3.67</v>
@@ -5883,28 +5883,28 @@
         <v>1.479</v>
       </c>
       <c r="M53">
-        <v>0.453358788</v>
+        <v>0.462248176</v>
       </c>
       <c r="N53">
-        <v>1.025641212</v>
+        <v>1.016751824</v>
       </c>
       <c r="O53">
-        <v>0.2461538908799999</v>
+        <v>0.24402043776</v>
       </c>
       <c r="P53">
-        <v>0.7794873211199999</v>
+        <v>0.77273138624</v>
       </c>
       <c r="Q53">
-        <v>1.24048732112</v>
+        <v>1.23373138624</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1953071696974098</v>
+        <v>0.1980045225387297</v>
       </c>
       <c r="T53">
-        <v>2.058022466128485</v>
+        <v>2.095152543286303</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.262316820910506</v>
+        <v>3.199579958969919</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1203744908185902</v>
+        <v>0.1202033084854497</v>
       </c>
       <c r="C54">
-        <v>7.276946756220963</v>
+        <v>7.151216859832593</v>
       </c>
       <c r="D54">
-        <v>10.81830675622096</v>
+        <v>10.83125685983259</v>
       </c>
       <c r="E54">
-        <v>6.84336</v>
+        <v>6.98204</v>
       </c>
       <c r="F54">
-        <v>7.21136</v>
+        <v>7.350040000000001</v>
       </c>
       <c r="G54">
         <v>3.67</v>
@@ -5965,28 +5965,28 @@
         <v>1.479</v>
       </c>
       <c r="M54">
-        <v>0.462248176</v>
+        <v>0.4711375640000001</v>
       </c>
       <c r="N54">
-        <v>1.016751824</v>
+        <v>1.007862436</v>
       </c>
       <c r="O54">
-        <v>0.24402043776</v>
+        <v>0.24188698464</v>
       </c>
       <c r="P54">
-        <v>0.77273138624</v>
+        <v>0.7659754513599999</v>
       </c>
       <c r="Q54">
-        <v>1.23373138624</v>
+        <v>1.22697545136</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1980045225387297</v>
+        <v>0.2008166563520206</v>
       </c>
       <c r="T54">
-        <v>2.095152543286303</v>
+        <v>2.133862623727433</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.199579958969919</v>
+        <v>3.139210525781807</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6011,22 +6011,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1202033084854497</v>
+        <v>0.1200321261523091</v>
       </c>
       <c r="C55">
-        <v>7.151216859832593</v>
+        <v>7.025518004563725</v>
       </c>
       <c r="D55">
-        <v>10.83125685983259</v>
+        <v>10.84423800456373</v>
       </c>
       <c r="E55">
-        <v>6.98204</v>
+        <v>7.12072</v>
       </c>
       <c r="F55">
-        <v>7.350040000000001</v>
+        <v>7.488720000000001</v>
       </c>
       <c r="G55">
         <v>3.67</v>
@@ -6047,28 +6047,28 @@
         <v>1.479</v>
       </c>
       <c r="M55">
-        <v>0.4711375640000001</v>
+        <v>0.4800269520000001</v>
       </c>
       <c r="N55">
-        <v>1.007862436</v>
+        <v>0.9989730479999999</v>
       </c>
       <c r="O55">
-        <v>0.24188698464</v>
+        <v>0.23975353152</v>
       </c>
       <c r="P55">
-        <v>0.7659754513599999</v>
+        <v>0.75921951648</v>
       </c>
       <c r="Q55">
-        <v>1.22697545136</v>
+        <v>1.22021951648</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2008166563520206</v>
+        <v>0.2037510568528459</v>
       </c>
       <c r="T55">
-        <v>2.133862623727433</v>
+        <v>2.174255751144263</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.139210525781807</v>
+        <v>3.081076997526588</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6093,22 +6093,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1200321261523091</v>
+        <v>0.1198609438191686</v>
       </c>
       <c r="C56">
-        <v>7.025518004563725</v>
+        <v>6.899850302155621</v>
       </c>
       <c r="D56">
-        <v>10.84423800456373</v>
+        <v>10.85725030215562</v>
       </c>
       <c r="E56">
-        <v>7.12072</v>
+        <v>7.2594</v>
       </c>
       <c r="F56">
-        <v>7.488720000000001</v>
+        <v>7.627400000000001</v>
       </c>
       <c r="G56">
         <v>3.67</v>
@@ -6129,28 +6129,28 @@
         <v>1.479</v>
       </c>
       <c r="M56">
-        <v>0.4800269520000001</v>
+        <v>0.4889163400000001</v>
       </c>
       <c r="N56">
-        <v>0.9989730479999999</v>
+        <v>0.9900836599999998</v>
       </c>
       <c r="O56">
-        <v>0.23975353152</v>
+        <v>0.2376200783999999</v>
       </c>
       <c r="P56">
-        <v>0.75921951648</v>
+        <v>0.7524635815999998</v>
       </c>
       <c r="Q56">
-        <v>1.22021951648</v>
+        <v>1.2134635816</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2037510568528459</v>
+        <v>0.2068158751537079</v>
       </c>
       <c r="T56">
-        <v>2.174255751144263</v>
+        <v>2.216444128668508</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.081076997526588</v>
+        <v>3.025057415753377</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6175,22 +6175,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1198609438191686</v>
+        <v>0.123009441486028</v>
       </c>
       <c r="C57">
-        <v>6.899850302155621</v>
+        <v>6.526726555235005</v>
       </c>
       <c r="D57">
-        <v>10.85725030215562</v>
+        <v>10.62280655523501</v>
       </c>
       <c r="E57">
-        <v>7.2594</v>
+        <v>7.39808</v>
       </c>
       <c r="F57">
-        <v>7.627400000000001</v>
+        <v>7.766080000000001</v>
       </c>
       <c r="G57">
         <v>3.67</v>
@@ -6211,45 +6211,45 @@
         <v>1.479</v>
       </c>
       <c r="M57">
-        <v>0.4889163400000001</v>
+        <v>0.558381152</v>
       </c>
       <c r="N57">
-        <v>0.9900836599999998</v>
+        <v>0.9206188479999998</v>
       </c>
       <c r="O57">
-        <v>0.2376200783999999</v>
+        <v>0.2209485235199999</v>
       </c>
       <c r="P57">
-        <v>0.7524635815999998</v>
+        <v>0.6996703244799999</v>
       </c>
       <c r="Q57">
-        <v>1.2134635816</v>
+        <v>1.16067032448</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2068158751537079</v>
+        <v>0.2100200033773363</v>
       </c>
       <c r="T57">
-        <v>2.216444128668508</v>
+        <v>2.260550159716583</v>
       </c>
       <c r="U57">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V57">
         <v>0.24</v>
       </c>
       <c r="W57">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.025057415753377</v>
+        <v>2.648728372550798</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6257,22 +6257,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.123009441486028</v>
+        <v>0.1228975391528874</v>
       </c>
       <c r="C58">
-        <v>6.526726555235005</v>
+        <v>6.396205373753627</v>
       </c>
       <c r="D58">
-        <v>10.62280655523501</v>
+        <v>10.63096537375363</v>
       </c>
       <c r="E58">
-        <v>7.39808</v>
+        <v>7.536760000000001</v>
       </c>
       <c r="F58">
-        <v>7.766080000000001</v>
+        <v>7.904760000000001</v>
       </c>
       <c r="G58">
         <v>3.67</v>
@@ -6293,28 +6293,28 @@
         <v>1.479</v>
       </c>
       <c r="M58">
-        <v>0.558381152</v>
+        <v>0.5683522440000002</v>
       </c>
       <c r="N58">
-        <v>0.9206188479999998</v>
+        <v>0.9106477559999997</v>
       </c>
       <c r="O58">
-        <v>0.2209485235199999</v>
+        <v>0.2185554614399999</v>
       </c>
       <c r="P58">
-        <v>0.6996703244799999</v>
+        <v>0.6920922945599998</v>
       </c>
       <c r="Q58">
-        <v>1.16067032448</v>
+        <v>1.15309229456</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2100200033773363</v>
+        <v>0.2133731608206685</v>
       </c>
       <c r="T58">
-        <v>2.260550159716583</v>
+        <v>2.306707634069219</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.648728372550798</v>
+        <v>2.602259453734117</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6339,22 +6339,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1228975391528874</v>
+        <v>0.1227856368197469</v>
       </c>
       <c r="C59">
-        <v>6.396205373753627</v>
+        <v>6.265696734623402</v>
       </c>
       <c r="D59">
-        <v>10.63096537375363</v>
+        <v>10.6391367346234</v>
       </c>
       <c r="E59">
-        <v>7.536760000000001</v>
+        <v>7.67544</v>
       </c>
       <c r="F59">
-        <v>7.904760000000001</v>
+        <v>8.04344</v>
       </c>
       <c r="G59">
         <v>3.67</v>
@@ -6375,28 +6375,28 @@
         <v>1.479</v>
       </c>
       <c r="M59">
-        <v>0.5683522440000002</v>
+        <v>0.5783233360000001</v>
       </c>
       <c r="N59">
-        <v>0.9106477559999997</v>
+        <v>0.9006766639999998</v>
       </c>
       <c r="O59">
-        <v>0.2185554614399999</v>
+        <v>0.21616239936</v>
       </c>
       <c r="P59">
-        <v>0.6920922945599998</v>
+        <v>0.6845142646399999</v>
       </c>
       <c r="Q59">
-        <v>1.15309229456</v>
+        <v>1.14551426464</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2133731608206685</v>
+        <v>0.2168859924279688</v>
       </c>
       <c r="T59">
-        <v>2.306707634069219</v>
+        <v>2.355063083391029</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.602259453734117</v>
+        <v>2.557392911428356</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6421,22 +6421,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1227856368197469</v>
+        <v>0.1226737344866063</v>
       </c>
       <c r="C60">
-        <v>6.265696734623399</v>
+        <v>6.135200666788142</v>
       </c>
       <c r="D60">
-        <v>10.6391367346234</v>
+        <v>10.64732066678814</v>
       </c>
       <c r="E60">
-        <v>7.67544</v>
+        <v>7.814119999999999</v>
       </c>
       <c r="F60">
-        <v>8.04344</v>
+        <v>8.182119999999999</v>
       </c>
       <c r="G60">
         <v>3.67</v>
@@ -6457,28 +6457,28 @@
         <v>1.479</v>
       </c>
       <c r="M60">
-        <v>0.5783233360000001</v>
+        <v>0.588294428</v>
       </c>
       <c r="N60">
-        <v>0.9006766639999998</v>
+        <v>0.8907055719999999</v>
       </c>
       <c r="O60">
-        <v>0.21616239936</v>
+        <v>0.21376933728</v>
       </c>
       <c r="P60">
-        <v>0.6845142646399999</v>
+        <v>0.6769362347199999</v>
       </c>
       <c r="Q60">
-        <v>1.14551426464</v>
+        <v>1.13793623472</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2168859924279688</v>
+        <v>0.2205701816746496</v>
       </c>
       <c r="T60">
-        <v>2.355063083391029</v>
+        <v>2.40577733511878</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.557392911428356</v>
+        <v>2.514047268861774</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6503,22 +6503,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1226737344866063</v>
+        <v>0.1243402321534658</v>
       </c>
       <c r="C61">
-        <v>6.135200666788142</v>
+        <v>5.875929729274578</v>
       </c>
       <c r="D61">
-        <v>10.64732066678814</v>
+        <v>10.52672972927458</v>
       </c>
       <c r="E61">
-        <v>7.814119999999999</v>
+        <v>7.9528</v>
       </c>
       <c r="F61">
-        <v>8.182119999999999</v>
+        <v>8.3208</v>
       </c>
       <c r="G61">
         <v>3.67</v>
@@ -6539,45 +6539,45 @@
         <v>1.479</v>
       </c>
       <c r="M61">
-        <v>0.588294428</v>
+        <v>0.6307166400000001</v>
       </c>
       <c r="N61">
-        <v>0.8907055719999999</v>
+        <v>0.8482833599999998</v>
       </c>
       <c r="O61">
-        <v>0.21376933728</v>
+        <v>0.2035880063999999</v>
       </c>
       <c r="P61">
-        <v>0.6769362347199999</v>
+        <v>0.6446953535999999</v>
       </c>
       <c r="Q61">
-        <v>1.13793623472</v>
+        <v>1.1056953536</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2205701816746496</v>
+        <v>0.2244385803836644</v>
       </c>
       <c r="T61">
-        <v>2.40577733511878</v>
+        <v>2.459027299432918</v>
       </c>
       <c r="U61">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V61">
         <v>0.24</v>
       </c>
       <c r="W61">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.514047268861774</v>
+        <v>2.344951609331252</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6585,22 +6585,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1243402321534658</v>
+        <v>0.1242579698203252</v>
       </c>
       <c r="C62">
-        <v>5.875929729274578</v>
+        <v>5.743138260665715</v>
       </c>
       <c r="D62">
-        <v>10.52672972927458</v>
+        <v>10.53261826066571</v>
       </c>
       <c r="E62">
-        <v>7.9528</v>
+        <v>8.091479999999999</v>
       </c>
       <c r="F62">
-        <v>8.3208</v>
+        <v>8.459479999999999</v>
       </c>
       <c r="G62">
         <v>3.67</v>
@@ -6621,28 +6621,28 @@
         <v>1.479</v>
       </c>
       <c r="M62">
-        <v>0.6307166400000001</v>
+        <v>0.641228584</v>
       </c>
       <c r="N62">
-        <v>0.8482833599999998</v>
+        <v>0.8377714159999998</v>
       </c>
       <c r="O62">
-        <v>0.2035880063999999</v>
+        <v>0.20106513984</v>
       </c>
       <c r="P62">
-        <v>0.6446953535999999</v>
+        <v>0.6367062761599999</v>
       </c>
       <c r="Q62">
-        <v>1.1056953536</v>
+        <v>1.09770627616</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2244385803836644</v>
+        <v>0.2285053585136544</v>
       </c>
       <c r="T62">
-        <v>2.459027299432918</v>
+        <v>2.515008031147782</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.344951609331252</v>
+        <v>2.306509779670084</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6667,22 +6667,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1242579698203252</v>
+        <v>0.1241757074871847</v>
       </c>
       <c r="C63">
-        <v>5.743138260665715</v>
+        <v>5.610353383697447</v>
       </c>
       <c r="D63">
-        <v>10.53261826066571</v>
+        <v>10.53851338369745</v>
       </c>
       <c r="E63">
-        <v>8.091479999999999</v>
+        <v>8.23016</v>
       </c>
       <c r="F63">
-        <v>8.459479999999999</v>
+        <v>8.59816</v>
       </c>
       <c r="G63">
         <v>3.67</v>
@@ -6703,28 +6703,28 @@
         <v>1.479</v>
       </c>
       <c r="M63">
-        <v>0.641228584</v>
+        <v>0.651740528</v>
       </c>
       <c r="N63">
-        <v>0.8377714159999998</v>
+        <v>0.8272594719999998</v>
       </c>
       <c r="O63">
-        <v>0.20106513984</v>
+        <v>0.19854227328</v>
       </c>
       <c r="P63">
-        <v>0.6367062761599999</v>
+        <v>0.6287171987199999</v>
       </c>
       <c r="Q63">
-        <v>1.09770627616</v>
+        <v>1.08971719872</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2285053585136544</v>
+        <v>0.2327861775978544</v>
       </c>
       <c r="T63">
-        <v>2.515008031147782</v>
+        <v>2.573935117163429</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.306509779670084</v>
+        <v>2.269308009030244</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6749,22 +6749,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1241757074871847</v>
+        <v>0.1240934451540441</v>
       </c>
       <c r="C64">
-        <v>5.610353383697447</v>
+        <v>5.477575109444022</v>
       </c>
       <c r="D64">
-        <v>10.53851338369745</v>
+        <v>10.54441510944402</v>
       </c>
       <c r="E64">
-        <v>8.23016</v>
+        <v>8.368840000000001</v>
       </c>
       <c r="F64">
-        <v>8.59816</v>
+        <v>8.736840000000001</v>
       </c>
       <c r="G64">
         <v>3.67</v>
@@ -6785,28 +6785,28 @@
         <v>1.479</v>
       </c>
       <c r="M64">
-        <v>0.651740528</v>
+        <v>0.6622524720000001</v>
       </c>
       <c r="N64">
-        <v>0.8272594719999998</v>
+        <v>0.8167475279999997</v>
       </c>
       <c r="O64">
-        <v>0.19854227328</v>
+        <v>0.1960194067199999</v>
       </c>
       <c r="P64">
-        <v>0.6287171987199999</v>
+        <v>0.6207281212799998</v>
       </c>
       <c r="Q64">
-        <v>1.08971719872</v>
+        <v>1.08172812128</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2327861775978544</v>
+        <v>0.2372983923082272</v>
       </c>
       <c r="T64">
-        <v>2.573935117163429</v>
+        <v>2.636047451071812</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.269308009030244</v>
+        <v>2.233287246982144</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6831,22 +6831,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1240934451540441</v>
+        <v>0.1240111828209035</v>
       </c>
       <c r="C65">
-        <v>5.477575109444022</v>
+        <v>5.344803449004514</v>
       </c>
       <c r="D65">
-        <v>10.54441510944402</v>
+        <v>10.55032344900451</v>
       </c>
       <c r="E65">
-        <v>8.368840000000001</v>
+        <v>8.50752</v>
       </c>
       <c r="F65">
-        <v>8.736840000000001</v>
+        <v>8.87552</v>
       </c>
       <c r="G65">
         <v>3.67</v>
@@ -6867,28 +6867,28 @@
         <v>1.479</v>
       </c>
       <c r="M65">
-        <v>0.6622524720000001</v>
+        <v>0.672764416</v>
       </c>
       <c r="N65">
-        <v>0.8167475279999997</v>
+        <v>0.8062355839999998</v>
       </c>
       <c r="O65">
-        <v>0.1960194067199999</v>
+        <v>0.19349654016</v>
       </c>
       <c r="P65">
-        <v>0.6207281212799998</v>
+        <v>0.6127390438399999</v>
       </c>
       <c r="Q65">
-        <v>1.08172812128</v>
+        <v>1.07373904384</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2372983923082272</v>
+        <v>0.2420612856136209</v>
       </c>
       <c r="T65">
-        <v>2.636047451071812</v>
+        <v>2.701610470197329</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.233287246982144</v>
+        <v>2.198392133748048</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6913,22 +6913,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1240111828209035</v>
+        <v>0.123928920487763</v>
       </c>
       <c r="C66">
-        <v>5.344803449004514</v>
+        <v>5.212038413502887</v>
       </c>
       <c r="D66">
-        <v>10.55032344900451</v>
+        <v>10.55623841350289</v>
       </c>
       <c r="E66">
-        <v>8.50752</v>
+        <v>8.6462</v>
       </c>
       <c r="F66">
-        <v>8.87552</v>
+        <v>9.014200000000001</v>
       </c>
       <c r="G66">
         <v>3.67</v>
@@ -6949,28 +6949,28 @@
         <v>1.479</v>
       </c>
       <c r="M66">
-        <v>0.672764416</v>
+        <v>0.6832763600000001</v>
       </c>
       <c r="N66">
-        <v>0.8062355839999998</v>
+        <v>0.7957236399999997</v>
       </c>
       <c r="O66">
-        <v>0.19349654016</v>
+        <v>0.1909736735999999</v>
       </c>
       <c r="P66">
-        <v>0.6127390438399999</v>
+        <v>0.6047499663999998</v>
       </c>
       <c r="Q66">
-        <v>1.07373904384</v>
+        <v>1.0657499664</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2420612856136209</v>
+        <v>0.2470963442507514</v>
       </c>
       <c r="T66">
-        <v>2.701610470197329</v>
+        <v>2.77091994755859</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.198392133748048</v>
+        <v>2.164570716305771</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6995,22 +6995,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.123928920487763</v>
+        <v>0.1238466581546224</v>
       </c>
       <c r="C67">
-        <v>5.212038413502887</v>
+        <v>5.07928001408807</v>
       </c>
       <c r="D67">
-        <v>10.55623841350289</v>
+        <v>10.56216001408807</v>
       </c>
       <c r="E67">
-        <v>8.6462</v>
+        <v>8.784880000000001</v>
       </c>
       <c r="F67">
-        <v>9.014200000000001</v>
+        <v>9.152880000000001</v>
       </c>
       <c r="G67">
         <v>3.67</v>
@@ -7031,28 +7031,28 @@
         <v>1.479</v>
       </c>
       <c r="M67">
-        <v>0.6832763600000001</v>
+        <v>0.6937883040000001</v>
       </c>
       <c r="N67">
-        <v>0.7957236399999997</v>
+        <v>0.7852116959999997</v>
       </c>
       <c r="O67">
-        <v>0.1909736735999999</v>
+        <v>0.1884508070399999</v>
       </c>
       <c r="P67">
-        <v>0.6047499663999998</v>
+        <v>0.5967608889599998</v>
       </c>
       <c r="Q67">
-        <v>1.0657499664</v>
+        <v>1.05776088896</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2470963442507514</v>
+        <v>0.252427582807713</v>
       </c>
       <c r="T67">
-        <v>2.77091994755859</v>
+        <v>2.844306452999924</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.164570716305771</v>
+        <v>2.131774190301138</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7077,22 +7077,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1238466581546224</v>
+        <v>0.1237643958214819</v>
       </c>
       <c r="C68">
-        <v>5.07928001408807</v>
+        <v>4.946528261934017</v>
       </c>
       <c r="D68">
-        <v>10.56216001408807</v>
+        <v>10.56808826193402</v>
       </c>
       <c r="E68">
-        <v>8.784880000000001</v>
+        <v>8.92356</v>
       </c>
       <c r="F68">
-        <v>9.152880000000001</v>
+        <v>9.29156</v>
       </c>
       <c r="G68">
         <v>3.67</v>
@@ -7113,28 +7113,28 @@
         <v>1.479</v>
       </c>
       <c r="M68">
-        <v>0.6937883040000001</v>
+        <v>0.7043002480000001</v>
       </c>
       <c r="N68">
-        <v>0.7852116959999997</v>
+        <v>0.7746997519999997</v>
       </c>
       <c r="O68">
-        <v>0.1884508070399999</v>
+        <v>0.1859279404799999</v>
       </c>
       <c r="P68">
-        <v>0.5967608889599998</v>
+        <v>0.5887718115199998</v>
       </c>
       <c r="Q68">
-        <v>1.05776088896</v>
+        <v>1.04977181152</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.252427582807713</v>
+        <v>0.2580819267317632</v>
       </c>
       <c r="T68">
-        <v>2.844306452999924</v>
+        <v>2.922140625437703</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.131774190301138</v>
+        <v>2.099956665072763</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7159,22 +7159,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1237643958214819</v>
+        <v>0.1236821334883413</v>
       </c>
       <c r="C69">
-        <v>4.946528261934017</v>
+        <v>4.813783168239777</v>
       </c>
       <c r="D69">
-        <v>10.56808826193402</v>
+        <v>10.57402316823978</v>
       </c>
       <c r="E69">
-        <v>8.92356</v>
+        <v>9.062240000000001</v>
       </c>
       <c r="F69">
-        <v>9.29156</v>
+        <v>9.430240000000001</v>
       </c>
       <c r="G69">
         <v>3.67</v>
@@ -7195,28 +7195,28 @@
         <v>1.479</v>
       </c>
       <c r="M69">
-        <v>0.7043002480000001</v>
+        <v>0.7148121920000001</v>
       </c>
       <c r="N69">
-        <v>0.7746997519999997</v>
+        <v>0.7641878079999997</v>
       </c>
       <c r="O69">
-        <v>0.1859279404799999</v>
+        <v>0.1834050739199999</v>
       </c>
       <c r="P69">
-        <v>0.5887718115199998</v>
+        <v>0.5807827340799998</v>
       </c>
       <c r="Q69">
-        <v>1.04977181152</v>
+        <v>1.04178273408</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2580819267317632</v>
+        <v>0.2640896671510666</v>
       </c>
       <c r="T69">
-        <v>2.922140625437703</v>
+        <v>3.004839433652843</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.099956665072763</v>
+        <v>2.069074949409928</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7241,22 +7241,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1236821334883413</v>
+        <v>0.1235998711552008</v>
       </c>
       <c r="C70">
-        <v>4.813783168239777</v>
+        <v>4.681044744229585</v>
       </c>
       <c r="D70">
-        <v>10.57402316823978</v>
+        <v>10.57996474422958</v>
       </c>
       <c r="E70">
-        <v>9.062240000000001</v>
+        <v>9.20092</v>
       </c>
       <c r="F70">
-        <v>9.430240000000001</v>
+        <v>9.56892</v>
       </c>
       <c r="G70">
         <v>3.67</v>
@@ -7277,28 +7277,28 @@
         <v>1.479</v>
       </c>
       <c r="M70">
-        <v>0.7148121920000001</v>
+        <v>0.7253241360000001</v>
       </c>
       <c r="N70">
-        <v>0.7641878079999997</v>
+        <v>0.7536758639999998</v>
       </c>
       <c r="O70">
-        <v>0.1834050739199999</v>
+        <v>0.1808822073599999</v>
       </c>
       <c r="P70">
-        <v>0.5807827340799998</v>
+        <v>0.5727936566399998</v>
       </c>
       <c r="Q70">
-        <v>1.04178273408</v>
+        <v>1.03379365664</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2640896671510666</v>
+        <v>0.2704850037264541</v>
       </c>
       <c r="T70">
-        <v>3.004839433652843</v>
+        <v>3.092873648849605</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.069074949409928</v>
+        <v>2.039088355940219</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7323,22 +7323,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1235998711552008</v>
+        <v>0.1235176088220602</v>
       </c>
       <c r="C71">
-        <v>4.681044744229585</v>
+        <v>4.548313001152907</v>
       </c>
       <c r="D71">
-        <v>10.57996474422958</v>
+        <v>10.58591300115291</v>
       </c>
       <c r="E71">
-        <v>9.20092</v>
+        <v>9.339600000000001</v>
       </c>
       <c r="F71">
-        <v>9.56892</v>
+        <v>9.707600000000001</v>
       </c>
       <c r="G71">
         <v>3.67</v>
@@ -7359,28 +7359,28 @@
         <v>1.479</v>
       </c>
       <c r="M71">
-        <v>0.7253241360000001</v>
+        <v>0.7358360800000001</v>
       </c>
       <c r="N71">
-        <v>0.7536758639999998</v>
+        <v>0.7431639199999998</v>
       </c>
       <c r="O71">
-        <v>0.1808822073599999</v>
+        <v>0.1783593407999999</v>
       </c>
       <c r="P71">
-        <v>0.5727936566399998</v>
+        <v>0.5648045791999998</v>
       </c>
       <c r="Q71">
-        <v>1.03379365664</v>
+        <v>1.0258045792</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2704850037264541</v>
+        <v>0.277306696073534</v>
       </c>
       <c r="T71">
-        <v>3.092873648849605</v>
+        <v>3.186776811726151</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.039088355940219</v>
+        <v>2.00995852228393</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7405,22 +7405,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1235176088220602</v>
+        <v>0.1310976664889196</v>
       </c>
       <c r="C72">
-        <v>4.548313001152907</v>
+        <v>3.888234458333681</v>
       </c>
       <c r="D72">
-        <v>10.58591300115291</v>
+        <v>10.06451445833368</v>
       </c>
       <c r="E72">
-        <v>9.339600000000001</v>
+        <v>9.478280000000002</v>
       </c>
       <c r="F72">
-        <v>9.707600000000001</v>
+        <v>9.846280000000002</v>
       </c>
       <c r="G72">
         <v>3.67</v>
@@ -7441,45 +7441,45 @@
         <v>1.479</v>
       </c>
       <c r="M72">
-        <v>0.7358360800000001</v>
+        <v>0.8861652000000001</v>
       </c>
       <c r="N72">
-        <v>0.7431639199999998</v>
+        <v>0.5928347999999998</v>
       </c>
       <c r="O72">
-        <v>0.1783593407999999</v>
+        <v>0.1422803519999999</v>
       </c>
       <c r="P72">
-        <v>0.5648045791999998</v>
+        <v>0.4505544479999998</v>
       </c>
       <c r="Q72">
-        <v>1.0258045792</v>
+        <v>0.9115544479999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.277306696073534</v>
+        <v>0.2845988499617919</v>
       </c>
       <c r="T72">
-        <v>3.186776811726151</v>
+        <v>3.28715605480108</v>
       </c>
       <c r="U72">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V72">
         <v>0.24</v>
       </c>
       <c r="W72">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.00995852228393</v>
+        <v>1.668989032744684</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7487,22 +7487,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1310976664889196</v>
+        <v>0.131123324155779</v>
       </c>
       <c r="C73">
-        <v>3.888234458333683</v>
+        <v>3.747876788197908</v>
       </c>
       <c r="D73">
-        <v>10.06451445833368</v>
+        <v>10.06283678819791</v>
       </c>
       <c r="E73">
-        <v>9.47828</v>
+        <v>9.616959999999999</v>
       </c>
       <c r="F73">
-        <v>9.84628</v>
+        <v>9.984959999999999</v>
       </c>
       <c r="G73">
         <v>3.67</v>
@@ -7523,28 +7523,28 @@
         <v>1.479</v>
       </c>
       <c r="M73">
-        <v>0.8861652</v>
+        <v>0.8986463999999998</v>
       </c>
       <c r="N73">
-        <v>0.5928347999999999</v>
+        <v>0.5803536</v>
       </c>
       <c r="O73">
-        <v>0.142280352</v>
+        <v>0.139284864</v>
       </c>
       <c r="P73">
-        <v>0.4505544479999999</v>
+        <v>0.441068736</v>
       </c>
       <c r="Q73">
-        <v>0.911554448</v>
+        <v>0.902068736</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2845988499617918</v>
+        <v>0.2924118719849252</v>
       </c>
       <c r="T73">
-        <v>3.287156054801079</v>
+        <v>3.394705243809931</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.668989032744685</v>
+        <v>1.64580862951212</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7569,22 +7569,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.131123324155779</v>
+        <v>0.1311489818226385</v>
       </c>
       <c r="C74">
-        <v>3.747876788197908</v>
+        <v>3.607519677275992</v>
       </c>
       <c r="D74">
-        <v>10.06283678819791</v>
+        <v>10.06115967727599</v>
       </c>
       <c r="E74">
-        <v>9.616959999999999</v>
+        <v>9.75564</v>
       </c>
       <c r="F74">
-        <v>9.984959999999999</v>
+        <v>10.12364</v>
       </c>
       <c r="G74">
         <v>3.67</v>
@@ -7605,28 +7605,28 @@
         <v>1.479</v>
       </c>
       <c r="M74">
-        <v>0.8986463999999998</v>
+        <v>0.9111275999999999</v>
       </c>
       <c r="N74">
-        <v>0.5803536</v>
+        <v>0.5678723999999999</v>
       </c>
       <c r="O74">
-        <v>0.139284864</v>
+        <v>0.136289376</v>
       </c>
       <c r="P74">
-        <v>0.441068736</v>
+        <v>0.4315830239999999</v>
       </c>
       <c r="Q74">
-        <v>0.902068736</v>
+        <v>0.8925830239999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2924118719849252</v>
+        <v>0.3008036363801426</v>
       </c>
       <c r="T74">
-        <v>3.394705243809931</v>
+        <v>3.510221039412031</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.64580862951212</v>
+        <v>1.623263305820173</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7651,22 +7651,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1311489818226385</v>
+        <v>0.1311746394894979</v>
       </c>
       <c r="C75">
-        <v>3.607519677275992</v>
+        <v>3.46716312528838</v>
       </c>
       <c r="D75">
-        <v>10.06115967727599</v>
+        <v>10.05948312528838</v>
       </c>
       <c r="E75">
-        <v>9.75564</v>
+        <v>9.89432</v>
       </c>
       <c r="F75">
-        <v>10.12364</v>
+        <v>10.26232</v>
       </c>
       <c r="G75">
         <v>3.67</v>
@@ -7687,28 +7687,28 @@
         <v>1.479</v>
       </c>
       <c r="M75">
-        <v>0.9111275999999999</v>
+        <v>0.9236088</v>
       </c>
       <c r="N75">
-        <v>0.5678723999999999</v>
+        <v>0.5553911999999999</v>
       </c>
       <c r="O75">
-        <v>0.136289376</v>
+        <v>0.133293888</v>
       </c>
       <c r="P75">
-        <v>0.4315830239999999</v>
+        <v>0.4220973119999999</v>
       </c>
       <c r="Q75">
-        <v>0.8925830239999999</v>
+        <v>0.8830973119999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3008036363801426</v>
+        <v>0.3098409211134536</v>
       </c>
       <c r="T75">
-        <v>3.510221039412031</v>
+        <v>3.634622665445061</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.623263305820173</v>
+        <v>1.601327315200981</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7733,22 +7733,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1311746394894979</v>
+        <v>0.1312002971563574</v>
       </c>
       <c r="C76">
-        <v>3.46716312528838</v>
+        <v>3.326807131955706</v>
       </c>
       <c r="D76">
-        <v>10.05948312528838</v>
+        <v>10.05780713195571</v>
       </c>
       <c r="E76">
-        <v>9.89432</v>
+        <v>10.033</v>
       </c>
       <c r="F76">
-        <v>10.26232</v>
+        <v>10.401</v>
       </c>
       <c r="G76">
         <v>3.67</v>
@@ -7769,28 +7769,28 @@
         <v>1.479</v>
       </c>
       <c r="M76">
-        <v>0.9236088</v>
+        <v>0.93609</v>
       </c>
       <c r="N76">
-        <v>0.5553911999999999</v>
+        <v>0.5429099999999999</v>
       </c>
       <c r="O76">
-        <v>0.133293888</v>
+        <v>0.1302984</v>
       </c>
       <c r="P76">
-        <v>0.4220973119999999</v>
+        <v>0.4126115999999999</v>
       </c>
       <c r="Q76">
-        <v>0.8830973119999999</v>
+        <v>0.8736115999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3098409211134536</v>
+        <v>0.3196011886254296</v>
       </c>
       <c r="T76">
-        <v>3.634622665445061</v>
+        <v>3.768976421560736</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.601327315200981</v>
+        <v>1.579976284331635</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7815,22 +7815,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1312002971563574</v>
+        <v>0.1312259548232168</v>
       </c>
       <c r="C77">
-        <v>3.326807131955706</v>
+        <v>3.186451696998784</v>
       </c>
       <c r="D77">
-        <v>10.05780713195571</v>
+        <v>10.05613169699878</v>
       </c>
       <c r="E77">
-        <v>10.033</v>
+        <v>10.17168</v>
       </c>
       <c r="F77">
-        <v>10.401</v>
+        <v>10.53968</v>
       </c>
       <c r="G77">
         <v>3.67</v>
@@ -7851,28 +7851,28 @@
         <v>1.479</v>
       </c>
       <c r="M77">
-        <v>0.93609</v>
+        <v>0.9485712000000001</v>
       </c>
       <c r="N77">
-        <v>0.5429099999999999</v>
+        <v>0.5304287999999998</v>
       </c>
       <c r="O77">
-        <v>0.1302984</v>
+        <v>0.127302912</v>
       </c>
       <c r="P77">
-        <v>0.4126115999999999</v>
+        <v>0.4031258879999998</v>
       </c>
       <c r="Q77">
-        <v>0.8736115999999999</v>
+        <v>0.8641258879999998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3196011886254296</v>
+        <v>0.3301748117634035</v>
       </c>
       <c r="T77">
-        <v>3.768976421560736</v>
+        <v>3.914526324019381</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.579976284331635</v>
+        <v>1.559187122695692</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7897,22 +7897,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1312259548232168</v>
+        <v>0.1312516124900763</v>
       </c>
       <c r="C78">
-        <v>3.186451696998784</v>
+        <v>3.04609682013862</v>
       </c>
       <c r="D78">
-        <v>10.05613169699878</v>
+        <v>10.05445682013862</v>
       </c>
       <c r="E78">
-        <v>10.17168</v>
+        <v>10.31036</v>
       </c>
       <c r="F78">
-        <v>10.53968</v>
+        <v>10.67836</v>
       </c>
       <c r="G78">
         <v>3.67</v>
@@ -7933,28 +7933,28 @@
         <v>1.479</v>
       </c>
       <c r="M78">
-        <v>0.9485712000000001</v>
+        <v>0.9610523999999999</v>
       </c>
       <c r="N78">
-        <v>0.5304287999999998</v>
+        <v>0.5179476</v>
       </c>
       <c r="O78">
-        <v>0.127302912</v>
+        <v>0.124307424</v>
       </c>
       <c r="P78">
-        <v>0.4031258879999998</v>
+        <v>0.393640176</v>
       </c>
       <c r="Q78">
-        <v>0.8641258879999998</v>
+        <v>0.854640176</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3301748117634035</v>
+        <v>0.341667880391636</v>
       </c>
       <c r="T78">
-        <v>3.914526324019381</v>
+        <v>4.072732739735302</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.559187122695692</v>
+        <v>1.53893793928406</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7979,22 +7979,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1312516124900763</v>
+        <v>0.1312772701569357</v>
       </c>
       <c r="C79">
-        <v>3.04609682013862</v>
+        <v>2.905742501096402</v>
       </c>
       <c r="D79">
-        <v>10.05445682013862</v>
+        <v>10.0527825010964</v>
       </c>
       <c r="E79">
-        <v>10.31036</v>
+        <v>10.44904</v>
       </c>
       <c r="F79">
-        <v>10.67836</v>
+        <v>10.81704</v>
       </c>
       <c r="G79">
         <v>3.67</v>
@@ -8015,28 +8015,28 @@
         <v>1.479</v>
       </c>
       <c r="M79">
-        <v>0.9610523999999999</v>
+        <v>0.9735336</v>
       </c>
       <c r="N79">
-        <v>0.5179476</v>
+        <v>0.5054663999999999</v>
       </c>
       <c r="O79">
-        <v>0.124307424</v>
+        <v>0.121311936</v>
       </c>
       <c r="P79">
-        <v>0.393640176</v>
+        <v>0.3841544639999999</v>
       </c>
       <c r="Q79">
-        <v>0.854640176</v>
+        <v>0.8451544639999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.341667880391636</v>
+        <v>0.3542057734406169</v>
       </c>
       <c r="T79">
-        <v>4.072732739735302</v>
+        <v>4.245321556879942</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.53893793928406</v>
+        <v>1.519207965703495</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8061,22 +8061,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1312772701569357</v>
+        <v>0.168915731594645</v>
       </c>
       <c r="C80">
-        <v>2.905742501096402</v>
+        <v>0.7934530578021644</v>
       </c>
       <c r="D80">
-        <v>10.0527825010964</v>
+        <v>8.079173057802166</v>
       </c>
       <c r="E80">
-        <v>10.44904</v>
+        <v>10.58772</v>
       </c>
       <c r="F80">
-        <v>10.81704</v>
+        <v>10.95572</v>
       </c>
       <c r="G80">
         <v>3.67</v>
@@ -8097,45 +8097,45 @@
         <v>1.479</v>
       </c>
       <c r="M80">
-        <v>0.9735336</v>
+        <v>1.608299696</v>
       </c>
       <c r="N80">
-        <v>0.5054663999999999</v>
+        <v>-0.1292996960000004</v>
       </c>
       <c r="O80">
-        <v>0.121311936</v>
+        <v>-0.03103192704000008</v>
       </c>
       <c r="P80">
-        <v>0.3841544639999999</v>
+        <v>-0.09826776896000027</v>
       </c>
       <c r="Q80">
-        <v>0.8451544639999999</v>
+        <v>0.3627322310399997</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3542057734406169</v>
+        <v>0.373996892384845</v>
       </c>
       <c r="T80">
-        <v>4.245321556879942</v>
+        <v>4.517753758623027</v>
       </c>
       <c r="U80">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.24</v>
+        <v>0.2207051340510854</v>
       </c>
       <c r="W80">
-        <v>0.0684</v>
+        <v>0.1144004863213007</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.519207965703495</v>
+        <v>0.9196047252128559</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8143,22 +8143,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.168915731594645</v>
+        <v>0.169925731594645</v>
       </c>
       <c r="C81">
-        <v>0.7934530578021644</v>
+        <v>0.61243320006243</v>
       </c>
       <c r="D81">
-        <v>8.079173057802166</v>
+        <v>8.03683320006243</v>
       </c>
       <c r="E81">
-        <v>10.58772</v>
+        <v>10.7264</v>
       </c>
       <c r="F81">
-        <v>10.95572</v>
+        <v>11.0944</v>
       </c>
       <c r="G81">
         <v>3.67</v>
@@ -8179,37 +8179,37 @@
         <v>1.479</v>
       </c>
       <c r="M81">
-        <v>1.608299696</v>
+        <v>1.62865792</v>
       </c>
       <c r="N81">
-        <v>-0.1292996960000004</v>
+        <v>-0.1496579200000003</v>
       </c>
       <c r="O81">
-        <v>-0.03103192704000008</v>
+        <v>-0.03591790080000008</v>
       </c>
       <c r="P81">
-        <v>-0.09826776896000027</v>
+        <v>-0.1137400192000003</v>
       </c>
       <c r="Q81">
-        <v>0.3627322310399997</v>
+        <v>0.3472599807999998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.373996892384845</v>
+        <v>0.3904067370040873</v>
       </c>
       <c r="T81">
-        <v>4.517753758623027</v>
+        <v>4.74364144655418</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2207051340510854</v>
+        <v>0.2179463198754468</v>
       </c>
       <c r="W81">
-        <v>0.1144004863213007</v>
+        <v>0.1148054802422844</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.9196047252128559</v>
+        <v>0.9081096661476952</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8225,22 +8225,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.169925731594645</v>
+        <v>0.170935731594645</v>
       </c>
       <c r="C82">
-        <v>0.61243320006243</v>
+        <v>0.4318548028170817</v>
       </c>
       <c r="D82">
-        <v>8.03683320006243</v>
+        <v>7.994934802817082</v>
       </c>
       <c r="E82">
-        <v>10.7264</v>
+        <v>10.86508</v>
       </c>
       <c r="F82">
-        <v>11.0944</v>
+        <v>11.23308</v>
       </c>
       <c r="G82">
         <v>3.67</v>
@@ -8261,37 +8261,37 @@
         <v>1.479</v>
       </c>
       <c r="M82">
-        <v>1.62865792</v>
+        <v>1.649016144</v>
       </c>
       <c r="N82">
-        <v>-0.1496579200000003</v>
+        <v>-0.1700161440000005</v>
       </c>
       <c r="O82">
-        <v>-0.03591790080000008</v>
+        <v>-0.04080387456000013</v>
       </c>
       <c r="P82">
-        <v>-0.1137400192000003</v>
+        <v>-0.1292122694400004</v>
       </c>
       <c r="Q82">
-        <v>0.3472599807999998</v>
+        <v>0.3317877305599996</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3904067370040873</v>
+        <v>0.4085439336885129</v>
       </c>
       <c r="T82">
-        <v>4.74364144655418</v>
+        <v>4.993306785846504</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2179463198754468</v>
+        <v>0.2152556245683425</v>
       </c>
       <c r="W82">
-        <v>0.1148054802422844</v>
+        <v>0.1152004743133673</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.9081096661476952</v>
+        <v>0.8968984357014272</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8307,22 +8307,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.170935731594645</v>
+        <v>0.171945731594645</v>
       </c>
       <c r="C83">
-        <v>0.4318548028170817</v>
+        <v>0.25171099748027</v>
       </c>
       <c r="D83">
-        <v>7.994934802817082</v>
+        <v>7.953470997480273</v>
       </c>
       <c r="E83">
-        <v>10.86508</v>
+        <v>11.00376</v>
       </c>
       <c r="F83">
-        <v>11.23308</v>
+        <v>11.37176</v>
       </c>
       <c r="G83">
         <v>3.67</v>
@@ -8343,37 +8343,37 @@
         <v>1.479</v>
       </c>
       <c r="M83">
-        <v>1.649016144</v>
+        <v>1.669374368</v>
       </c>
       <c r="N83">
-        <v>-0.1700161440000005</v>
+        <v>-0.1903743680000005</v>
       </c>
       <c r="O83">
-        <v>-0.04080387456000013</v>
+        <v>-0.04568984832000012</v>
       </c>
       <c r="P83">
-        <v>-0.1292122694400004</v>
+        <v>-0.1446845196800004</v>
       </c>
       <c r="Q83">
-        <v>0.3317877305599996</v>
+        <v>0.3163154803199996</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4085439336885129</v>
+        <v>0.4286963744489859</v>
       </c>
       <c r="T83">
-        <v>4.993306785846504</v>
+        <v>5.270712718393533</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2152556245683425</v>
+        <v>0.2126305559760457</v>
       </c>
       <c r="W83">
-        <v>0.1152004743133673</v>
+        <v>0.1155858343827165</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8968984357014272</v>
+        <v>0.8859606499001904</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8389,22 +8389,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.171945731594645</v>
+        <v>0.1729557315946449</v>
       </c>
       <c r="C84">
-        <v>0.25171099748027</v>
+        <v>0.07199505722005917</v>
       </c>
       <c r="D84">
-        <v>7.953470997480273</v>
+        <v>7.912435057220059</v>
       </c>
       <c r="E84">
-        <v>11.00376</v>
+        <v>11.14244</v>
       </c>
       <c r="F84">
-        <v>11.37176</v>
+        <v>11.51044</v>
       </c>
       <c r="G84">
         <v>3.67</v>
@@ -8425,37 +8425,37 @@
         <v>1.479</v>
       </c>
       <c r="M84">
-        <v>1.669374368</v>
+        <v>1.689732592</v>
       </c>
       <c r="N84">
-        <v>-0.1903743680000005</v>
+        <v>-0.2107325920000005</v>
       </c>
       <c r="O84">
-        <v>-0.04568984832000012</v>
+        <v>-0.05057582208000012</v>
       </c>
       <c r="P84">
-        <v>-0.1446845196800004</v>
+        <v>-0.1601567699200004</v>
       </c>
       <c r="Q84">
-        <v>0.3163154803199996</v>
+        <v>0.3008432300799996</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4286963744489859</v>
+        <v>0.4512196905930439</v>
       </c>
       <c r="T84">
-        <v>5.270712718393533</v>
+        <v>5.580754643004918</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2126305559760457</v>
+        <v>0.2100687420486234</v>
       </c>
       <c r="W84">
-        <v>0.1155858343827165</v>
+        <v>0.1159619086672621</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8859606499001904</v>
+        <v>0.8752864252025977</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8471,22 +8471,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1729557315946449</v>
+        <v>0.173965731594645</v>
       </c>
       <c r="C85">
-        <v>0.07199505722005917</v>
+        <v>-0.1072996066797405</v>
       </c>
       <c r="D85">
-        <v>7.912435057220059</v>
+        <v>7.87182039332026</v>
       </c>
       <c r="E85">
-        <v>11.14244</v>
+        <v>11.28112</v>
       </c>
       <c r="F85">
-        <v>11.51044</v>
+        <v>11.64912</v>
       </c>
       <c r="G85">
         <v>3.67</v>
@@ -8507,37 +8507,37 @@
         <v>1.479</v>
       </c>
       <c r="M85">
-        <v>1.689732592</v>
+        <v>1.710090816</v>
       </c>
       <c r="N85">
-        <v>-0.2107325920000005</v>
+        <v>-0.2310908160000005</v>
       </c>
       <c r="O85">
-        <v>-0.05057582208000012</v>
+        <v>-0.05546179584000011</v>
       </c>
       <c r="P85">
-        <v>-0.1601567699200004</v>
+        <v>-0.1756290201600004</v>
       </c>
       <c r="Q85">
-        <v>0.3008432300799996</v>
+        <v>0.2853709798399997</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4512196905930439</v>
+        <v>0.4765584212551093</v>
       </c>
       <c r="T85">
-        <v>5.580754643004918</v>
+        <v>5.929551808192726</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2100687420486234</v>
+        <v>0.2075679236909017</v>
       </c>
       <c r="W85">
-        <v>0.1159619086672621</v>
+        <v>0.1163290288021756</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8752864252025977</v>
+        <v>0.8648663487120907</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8553,22 +8553,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.173965731594645</v>
+        <v>0.174975731594645</v>
       </c>
       <c r="C86">
-        <v>-0.1072996066797387</v>
+        <v>-0.2861794483461679</v>
       </c>
       <c r="D86">
-        <v>7.87182039332026</v>
+        <v>7.831620551653832</v>
       </c>
       <c r="E86">
-        <v>11.28112</v>
+        <v>11.4198</v>
       </c>
       <c r="F86">
-        <v>11.64912</v>
+        <v>11.7878</v>
       </c>
       <c r="G86">
         <v>3.67</v>
@@ -8589,37 +8589,37 @@
         <v>1.479</v>
       </c>
       <c r="M86">
-        <v>1.710090816</v>
+        <v>1.73044904</v>
       </c>
       <c r="N86">
-        <v>-0.2310908160000003</v>
+        <v>-0.2514490400000005</v>
       </c>
       <c r="O86">
-        <v>-0.05546179584000006</v>
+        <v>-0.06034776960000011</v>
       </c>
       <c r="P86">
-        <v>-0.1756290201600002</v>
+        <v>-0.1911012704000004</v>
       </c>
       <c r="Q86">
-        <v>0.2853709798399998</v>
+        <v>0.2698987295999997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.476558421255109</v>
+        <v>0.5052756493387828</v>
       </c>
       <c r="T86">
-        <v>5.929551808192723</v>
+        <v>6.324855262072236</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2075679236909017</v>
+        <v>0.2051259481180676</v>
       </c>
       <c r="W86">
-        <v>0.1163290288021756</v>
+        <v>0.1166875108162677</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8648663487120907</v>
+        <v>0.8546914504919484</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8635,22 +8635,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.174975731594645</v>
+        <v>0.175985731594645</v>
       </c>
       <c r="C87">
-        <v>-0.2861794483461679</v>
+        <v>-0.464650790736302</v>
       </c>
       <c r="D87">
-        <v>7.831620551653832</v>
+        <v>7.791829209263697</v>
       </c>
       <c r="E87">
-        <v>11.4198</v>
+        <v>11.55848</v>
       </c>
       <c r="F87">
-        <v>11.7878</v>
+        <v>11.92648</v>
       </c>
       <c r="G87">
         <v>3.67</v>
@@ -8671,37 +8671,37 @@
         <v>1.479</v>
       </c>
       <c r="M87">
-        <v>1.73044904</v>
+        <v>1.750807264</v>
       </c>
       <c r="N87">
-        <v>-0.2514490400000005</v>
+        <v>-0.2718072640000002</v>
       </c>
       <c r="O87">
-        <v>-0.06034776960000011</v>
+        <v>-0.06523374336000005</v>
       </c>
       <c r="P87">
-        <v>-0.1911012704000004</v>
+        <v>-0.2065735206400002</v>
       </c>
       <c r="Q87">
-        <v>0.2698987295999997</v>
+        <v>0.2544264793599998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5052756493387828</v>
+        <v>0.5380953385772673</v>
       </c>
       <c r="T87">
-        <v>6.324855262072236</v>
+        <v>6.77663063793454</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2051259481180676</v>
+        <v>0.2027407626748343</v>
       </c>
       <c r="W87">
-        <v>0.1166875108162677</v>
+        <v>0.1170376560393343</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8546914504919484</v>
+        <v>0.8447531778118096</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8717,22 +8717,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.175985731594645</v>
+        <v>0.176995731594645</v>
       </c>
       <c r="C88">
-        <v>-0.464650790736302</v>
+        <v>-0.6427198289526732</v>
       </c>
       <c r="D88">
-        <v>7.791829209263697</v>
+        <v>7.752440171047327</v>
       </c>
       <c r="E88">
-        <v>11.55848</v>
+        <v>11.69716</v>
       </c>
       <c r="F88">
-        <v>11.92648</v>
+        <v>12.06516</v>
       </c>
       <c r="G88">
         <v>3.67</v>
@@ -8753,37 +8753,37 @@
         <v>1.479</v>
       </c>
       <c r="M88">
-        <v>1.750807264</v>
+        <v>1.771165488</v>
       </c>
       <c r="N88">
-        <v>-0.2718072640000002</v>
+        <v>-0.2921654880000004</v>
       </c>
       <c r="O88">
-        <v>-0.06523374336000005</v>
+        <v>-0.07011971712000009</v>
       </c>
       <c r="P88">
-        <v>-0.2065735206400002</v>
+        <v>-0.2220457708800003</v>
       </c>
       <c r="Q88">
-        <v>0.2544264793599998</v>
+        <v>0.2389542291199997</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5380953385772673</v>
+        <v>0.5759642107755186</v>
       </c>
       <c r="T88">
-        <v>6.77663063793454</v>
+        <v>7.297909917775658</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2027407626748343</v>
+        <v>0.2004104090808706</v>
       </c>
       <c r="W88">
-        <v>0.1170376560393343</v>
+        <v>0.1173797519469282</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8447531778118096</v>
+        <v>0.8350433711702945</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8799,22 +8799,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.176995731594645</v>
+        <v>0.1780057315946449</v>
       </c>
       <c r="C89">
-        <v>-0.6427198289526732</v>
+        <v>-0.8203926334586296</v>
       </c>
       <c r="D89">
-        <v>7.752440171047327</v>
+        <v>7.71344736654137</v>
       </c>
       <c r="E89">
-        <v>11.69716</v>
+        <v>11.83584</v>
       </c>
       <c r="F89">
-        <v>12.06516</v>
+        <v>12.20384</v>
       </c>
       <c r="G89">
         <v>3.67</v>
@@ -8835,37 +8835,37 @@
         <v>1.479</v>
       </c>
       <c r="M89">
-        <v>1.771165488</v>
+        <v>1.791523712</v>
       </c>
       <c r="N89">
-        <v>-0.2921654880000004</v>
+        <v>-0.3125237120000002</v>
       </c>
       <c r="O89">
-        <v>-0.07011971712000009</v>
+        <v>-0.07500569088000004</v>
       </c>
       <c r="P89">
-        <v>-0.2220457708800003</v>
+        <v>-0.2375180211200001</v>
       </c>
       <c r="Q89">
-        <v>0.2389542291199997</v>
+        <v>0.2234819788799999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5759642107755186</v>
+        <v>0.6201445616734785</v>
       </c>
       <c r="T89">
-        <v>7.297909917775658</v>
+        <v>7.906069077590296</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2004104090808706</v>
+        <v>0.1981330180685881</v>
       </c>
       <c r="W89">
-        <v>0.1173797519469282</v>
+        <v>0.1177140729475313</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8350433711702945</v>
+        <v>0.8255542419524503</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8881,22 +8881,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1780057315946449</v>
+        <v>0.179015731594645</v>
       </c>
       <c r="C90">
-        <v>-0.8203926334586296</v>
+        <v>-0.9976751531972035</v>
       </c>
       <c r="D90">
-        <v>7.71344736654137</v>
+        <v>7.674844846802797</v>
       </c>
       <c r="E90">
-        <v>11.83584</v>
+        <v>11.97452</v>
       </c>
       <c r="F90">
-        <v>12.20384</v>
+        <v>12.34252</v>
       </c>
       <c r="G90">
         <v>3.67</v>
@@ -8917,37 +8917,37 @@
         <v>1.479</v>
       </c>
       <c r="M90">
-        <v>1.791523712</v>
+        <v>1.811881936</v>
       </c>
       <c r="N90">
-        <v>-0.3125237120000002</v>
+        <v>-0.3328819360000004</v>
       </c>
       <c r="O90">
-        <v>-0.07500569088000004</v>
+        <v>-0.07989166464000008</v>
       </c>
       <c r="P90">
-        <v>-0.2375180211200001</v>
+        <v>-0.2529902713600003</v>
       </c>
       <c r="Q90">
-        <v>0.2234819788799999</v>
+        <v>0.2080097286399997</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6201445616734785</v>
+        <v>0.6723577036437949</v>
       </c>
       <c r="T90">
-        <v>7.906069077590296</v>
+        <v>8.624802630098506</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1981330180685881</v>
+        <v>0.1959068043824241</v>
       </c>
       <c r="W90">
-        <v>0.1177140729475313</v>
+        <v>0.1180408811166602</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8255542419524503</v>
+        <v>0.8162783515934339</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8963,22 +8963,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.179015731594645</v>
+        <v>0.180025731594645</v>
       </c>
       <c r="C91">
-        <v>-0.9976751531972035</v>
+        <v>-1.174573218616718</v>
       </c>
       <c r="D91">
-        <v>7.674844846802797</v>
+        <v>7.636626781383284</v>
       </c>
       <c r="E91">
-        <v>11.97452</v>
+        <v>12.1132</v>
       </c>
       <c r="F91">
-        <v>12.34252</v>
+        <v>12.4812</v>
       </c>
       <c r="G91">
         <v>3.67</v>
@@ -8999,37 +8999,37 @@
         <v>1.479</v>
       </c>
       <c r="M91">
-        <v>1.811881936</v>
+        <v>1.83224016</v>
       </c>
       <c r="N91">
-        <v>-0.3328819360000004</v>
+        <v>-0.3532401600000006</v>
       </c>
       <c r="O91">
-        <v>-0.07989166464000008</v>
+        <v>-0.08477763840000013</v>
       </c>
       <c r="P91">
-        <v>-0.2529902713600003</v>
+        <v>-0.2684625216000004</v>
       </c>
       <c r="Q91">
-        <v>0.2080097286399997</v>
+        <v>0.1925374783999996</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6723577036437949</v>
+        <v>0.7350134740081745</v>
       </c>
       <c r="T91">
-        <v>8.624802630098506</v>
+        <v>9.487282893108359</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1959068043824241</v>
+        <v>0.1937300621115083</v>
       </c>
       <c r="W91">
-        <v>0.1180408811166602</v>
+        <v>0.1183604268820306</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8162783515934339</v>
+        <v>0.8072085921312846</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9045,22 +9045,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.180025731594645</v>
+        <v>0.2340898239054937</v>
       </c>
       <c r="C92">
-        <v>-1.174573218616718</v>
+        <v>-2.920432002945452</v>
       </c>
       <c r="D92">
-        <v>7.636626781383284</v>
+        <v>6.029447997054549</v>
       </c>
       <c r="E92">
-        <v>12.1132</v>
+        <v>12.25188</v>
       </c>
       <c r="F92">
-        <v>12.4812</v>
+        <v>12.61988</v>
       </c>
       <c r="G92">
         <v>3.67</v>
@@ -9081,45 +9081,45 @@
         <v>1.479</v>
       </c>
       <c r="M92">
-        <v>1.83224016</v>
+        <v>2.534071904</v>
       </c>
       <c r="N92">
-        <v>-0.3532401600000006</v>
+        <v>-1.055071904</v>
       </c>
       <c r="O92">
-        <v>-0.08477763840000013</v>
+        <v>-0.2532172569600001</v>
       </c>
       <c r="P92">
-        <v>-0.2684625216000004</v>
+        <v>-0.8018546470400002</v>
       </c>
       <c r="Q92">
-        <v>0.1925374783999996</v>
+        <v>-0.3408546470400002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7350134740081745</v>
+        <v>0.8550826634629572</v>
       </c>
       <c r="T92">
-        <v>9.487282893108359</v>
+        <v>11.14008048059464</v>
       </c>
       <c r="U92">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1937300621115083</v>
+        <v>0.1400749518747673</v>
       </c>
       <c r="W92">
-        <v>0.1183604268820306</v>
+        <v>0.1726729496635467</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.8072085921312846</v>
+        <v>0.5836456328115305</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9127,22 +9127,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2340898239054937</v>
+        <v>0.2356398239054937</v>
       </c>
       <c r="C93">
-        <v>-2.920432002945452</v>
+        <v>-3.095273834725809</v>
       </c>
       <c r="D93">
-        <v>6.029447997054549</v>
+        <v>5.993286165274192</v>
       </c>
       <c r="E93">
-        <v>12.25188</v>
+        <v>12.39056</v>
       </c>
       <c r="F93">
-        <v>12.61988</v>
+        <v>12.75856</v>
       </c>
       <c r="G93">
         <v>3.67</v>
@@ -9163,37 +9163,37 @@
         <v>1.479</v>
       </c>
       <c r="M93">
-        <v>2.534071904</v>
+        <v>2.561918848</v>
       </c>
       <c r="N93">
-        <v>-1.055071904</v>
+        <v>-1.082918848</v>
       </c>
       <c r="O93">
-        <v>-0.2532172569600001</v>
+        <v>-0.2599005235200001</v>
       </c>
       <c r="P93">
-        <v>-0.8018546470400002</v>
+        <v>-0.8230183244800005</v>
       </c>
       <c r="Q93">
-        <v>-0.3408546470400002</v>
+        <v>-0.3620183244800004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8550826634629572</v>
+        <v>0.956242996395827</v>
       </c>
       <c r="T93">
-        <v>11.14008048059464</v>
+        <v>12.53259054066897</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1400749518747673</v>
+        <v>0.1385523980500415</v>
       </c>
       <c r="W93">
-        <v>0.1726729496635467</v>
+        <v>0.1729786784715517</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5836456328115305</v>
+        <v>0.5773016585418398</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9209,22 +9209,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2356398239054937</v>
+        <v>0.2371898239054937</v>
       </c>
       <c r="C94">
-        <v>-3.095273834725809</v>
+        <v>-3.269684488730277</v>
       </c>
       <c r="D94">
-        <v>5.993286165274192</v>
+        <v>5.957555511269724</v>
       </c>
       <c r="E94">
-        <v>12.39056</v>
+        <v>12.52924</v>
       </c>
       <c r="F94">
-        <v>12.75856</v>
+        <v>12.89724</v>
       </c>
       <c r="G94">
         <v>3.67</v>
@@ -9245,37 +9245,37 @@
         <v>1.479</v>
       </c>
       <c r="M94">
-        <v>2.561918848</v>
+        <v>2.589765792000001</v>
       </c>
       <c r="N94">
-        <v>-1.082918848</v>
+        <v>-1.110765792000001</v>
       </c>
       <c r="O94">
-        <v>-0.2599005235200001</v>
+        <v>-0.2665837900800002</v>
       </c>
       <c r="P94">
-        <v>-0.8230183244800005</v>
+        <v>-0.8441820019200006</v>
       </c>
       <c r="Q94">
-        <v>-0.3620183244800004</v>
+        <v>-0.3831820019200006</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.956242996395827</v>
+        <v>1.086306281595231</v>
       </c>
       <c r="T94">
-        <v>12.53259054066897</v>
+        <v>14.32296061790739</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1385523980500415</v>
+        <v>0.1370625873183207</v>
       </c>
       <c r="W94">
-        <v>0.1729786784715517</v>
+        <v>0.1732778324664812</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5773016585418398</v>
+        <v>0.5710941138263361</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9291,22 +9291,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2371898239054937</v>
+        <v>0.2387398239054937</v>
       </c>
       <c r="C95">
-        <v>-3.269684488730277</v>
+        <v>-3.443671631016709</v>
       </c>
       <c r="D95">
-        <v>5.957555511269724</v>
+        <v>5.922248368983291</v>
       </c>
       <c r="E95">
-        <v>12.52924</v>
+        <v>12.66792</v>
       </c>
       <c r="F95">
-        <v>12.89724</v>
+        <v>13.03592</v>
       </c>
       <c r="G95">
         <v>3.67</v>
@@ -9327,37 +9327,37 @@
         <v>1.479</v>
       </c>
       <c r="M95">
-        <v>2.589765792000001</v>
+        <v>2.617612736</v>
       </c>
       <c r="N95">
-        <v>-1.110765792000001</v>
+        <v>-1.138612736</v>
       </c>
       <c r="O95">
-        <v>-0.2665837900800002</v>
+        <v>-0.2732670566400001</v>
       </c>
       <c r="P95">
-        <v>-0.8441820019200006</v>
+        <v>-0.8653456793600003</v>
       </c>
       <c r="Q95">
-        <v>-0.3831820019200006</v>
+        <v>-0.4043456793600003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.086306281595231</v>
+        <v>1.259723995194437</v>
       </c>
       <c r="T95">
-        <v>14.32296061790739</v>
+        <v>16.71012072089196</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1370625873183207</v>
+        <v>0.1356044746872747</v>
       </c>
       <c r="W95">
-        <v>0.1732778324664812</v>
+        <v>0.1735706214827953</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5710941138263361</v>
+        <v>0.5650186445303114</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9373,22 +9373,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2387398239054937</v>
+        <v>0.2402898239054937</v>
       </c>
       <c r="C96">
-        <v>-3.443671631016709</v>
+        <v>-3.617242746983671</v>
       </c>
       <c r="D96">
-        <v>5.922248368983291</v>
+        <v>5.88735725301633</v>
       </c>
       <c r="E96">
-        <v>12.66792</v>
+        <v>12.8066</v>
       </c>
       <c r="F96">
-        <v>13.03592</v>
+        <v>13.1746</v>
       </c>
       <c r="G96">
         <v>3.67</v>
@@ -9409,37 +9409,37 @@
         <v>1.479</v>
       </c>
       <c r="M96">
-        <v>2.617612736</v>
+        <v>2.645459680000001</v>
       </c>
       <c r="N96">
-        <v>-1.138612736</v>
+        <v>-1.166459680000001</v>
       </c>
       <c r="O96">
-        <v>-0.2732670566400001</v>
+        <v>-0.2799503232000001</v>
       </c>
       <c r="P96">
-        <v>-0.8653456793600003</v>
+        <v>-0.8865093568000005</v>
       </c>
       <c r="Q96">
-        <v>-0.4043456793600003</v>
+        <v>-0.4255093568000005</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.259723995194437</v>
+        <v>1.502508794233325</v>
       </c>
       <c r="T96">
-        <v>16.71012072089196</v>
+        <v>20.05214486507036</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1356044746872747</v>
+        <v>0.1341770591642508</v>
       </c>
       <c r="W96">
-        <v>0.1735706214827953</v>
+        <v>0.1738572465198184</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5650186445303114</v>
+        <v>0.5590710798510449</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9455,22 +9455,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2402898239054937</v>
+        <v>0.2418398239054937</v>
       </c>
       <c r="C97">
-        <v>-3.617242746983671</v>
+        <v>-3.790405146661046</v>
       </c>
       <c r="D97">
-        <v>5.88735725301633</v>
+        <v>5.852874853338956</v>
       </c>
       <c r="E97">
-        <v>12.8066</v>
+        <v>12.94528</v>
       </c>
       <c r="F97">
-        <v>13.1746</v>
+        <v>13.31328</v>
       </c>
       <c r="G97">
         <v>3.67</v>
@@ -9491,37 +9491,37 @@
         <v>1.479</v>
       </c>
       <c r="M97">
-        <v>2.645459680000001</v>
+        <v>2.673306624</v>
       </c>
       <c r="N97">
-        <v>-1.166459680000001</v>
+        <v>-1.194306624</v>
       </c>
       <c r="O97">
-        <v>-0.2799503232000001</v>
+        <v>-0.2866335897600001</v>
       </c>
       <c r="P97">
-        <v>-0.8865093568000005</v>
+        <v>-0.9076730342400003</v>
       </c>
       <c r="Q97">
-        <v>-0.4255093568000005</v>
+        <v>-0.4466730342400003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.502508794233325</v>
+        <v>1.866685992791657</v>
       </c>
       <c r="T97">
-        <v>20.05214486507036</v>
+        <v>25.06518108133796</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1341770591642508</v>
+        <v>0.1327793814646232</v>
       </c>
       <c r="W97">
-        <v>0.1738572465198184</v>
+        <v>0.1741379002019037</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5590710798510449</v>
+        <v>0.5532474227692632</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9537,22 +9537,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2418398239054937</v>
+        <v>0.2433898239054937</v>
       </c>
       <c r="C98">
-        <v>-3.790405146661046</v>
+        <v>-3.963165969815837</v>
       </c>
       <c r="D98">
-        <v>5.852874853338956</v>
+        <v>5.818794030184163</v>
       </c>
       <c r="E98">
-        <v>12.94528</v>
+        <v>13.08396</v>
       </c>
       <c r="F98">
-        <v>13.31328</v>
+        <v>13.45196</v>
       </c>
       <c r="G98">
         <v>3.67</v>
@@ -9573,37 +9573,37 @@
         <v>1.479</v>
       </c>
       <c r="M98">
-        <v>2.673306624</v>
+        <v>2.701153568</v>
       </c>
       <c r="N98">
-        <v>-1.194306624</v>
+        <v>-1.222153568</v>
       </c>
       <c r="O98">
-        <v>-0.2866335897600001</v>
+        <v>-0.29331685632</v>
       </c>
       <c r="P98">
-        <v>-0.9076730342400003</v>
+        <v>-0.9288367116800001</v>
       </c>
       <c r="Q98">
-        <v>-0.4466730342400003</v>
+        <v>-0.4678367116800001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.866685992791652</v>
+        <v>2.473647990388869</v>
       </c>
       <c r="T98">
-        <v>25.0651810813379</v>
+        <v>33.42024144178387</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1327793814646232</v>
+        <v>0.1314105218618951</v>
       </c>
       <c r="W98">
-        <v>0.1741379002019037</v>
+        <v>0.1744127672101315</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5532474227692632</v>
+        <v>0.5475438410912297</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9619,22 +9619,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2433898239054937</v>
+        <v>0.2449398239054937</v>
       </c>
       <c r="C99">
-        <v>-3.963165969815837</v>
+        <v>-4.135532190880605</v>
       </c>
       <c r="D99">
-        <v>5.818794030184163</v>
+        <v>5.785107809119395</v>
       </c>
       <c r="E99">
-        <v>13.08396</v>
+        <v>13.22264</v>
       </c>
       <c r="F99">
-        <v>13.45196</v>
+        <v>13.59064</v>
       </c>
       <c r="G99">
         <v>3.67</v>
@@ -9655,37 +9655,37 @@
         <v>1.479</v>
       </c>
       <c r="M99">
-        <v>2.701153568</v>
+        <v>2.729000512</v>
       </c>
       <c r="N99">
-        <v>-1.222153568</v>
+        <v>-1.250000512</v>
       </c>
       <c r="O99">
-        <v>-0.29331685632</v>
+        <v>-0.3000001228800001</v>
       </c>
       <c r="P99">
-        <v>-0.9288367116800001</v>
+        <v>-0.9500003891200003</v>
       </c>
       <c r="Q99">
-        <v>-0.4678367116800001</v>
+        <v>-0.4890003891200003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.473647990388869</v>
+        <v>3.687571985583304</v>
       </c>
       <c r="T99">
-        <v>33.42024144178387</v>
+        <v>50.1303621626758</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1314105218618951</v>
+        <v>0.1300695981694268</v>
       </c>
       <c r="W99">
-        <v>0.1744127672101315</v>
+        <v>0.1746820246875791</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5475438410912297</v>
+        <v>0.5419566590392783</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9701,22 +9701,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2449398239054937</v>
+        <v>0.2464898239054937</v>
       </c>
       <c r="C100">
-        <v>-4.135532190880605</v>
+        <v>-4.307510623711698</v>
       </c>
       <c r="D100">
-        <v>5.785107809119395</v>
+        <v>5.751809376288302</v>
       </c>
       <c r="E100">
-        <v>13.22264</v>
+        <v>13.36132</v>
       </c>
       <c r="F100">
-        <v>13.59064</v>
+        <v>13.72932</v>
       </c>
       <c r="G100">
         <v>3.67</v>
@@ -9737,37 +9737,37 @@
         <v>1.479</v>
       </c>
       <c r="M100">
-        <v>2.729000512</v>
+        <v>2.756847456</v>
       </c>
       <c r="N100">
-        <v>-1.250000512</v>
+        <v>-1.277847456</v>
       </c>
       <c r="O100">
-        <v>-0.3000001228800001</v>
+        <v>-0.30668338944</v>
       </c>
       <c r="P100">
-        <v>-0.9500003891200003</v>
+        <v>-0.9711640665600001</v>
       </c>
       <c r="Q100">
-        <v>-0.4890003891200003</v>
+        <v>-0.51016406656</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.687571985583304</v>
+        <v>7.329343971166607</v>
       </c>
       <c r="T100">
-        <v>50.1303621626758</v>
+        <v>100.2607243253516</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1300695981694268</v>
+        <v>0.1287557638444831</v>
       </c>
       <c r="W100">
-        <v>0.1746820246875791</v>
+        <v>0.1749458426200278</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9775,91 +9775,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5419566590392783</v>
+        <v>0.5364823493520128</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2464898239054937</v>
-      </c>
-      <c r="C101">
-        <v>-4.307510623711698</v>
-      </c>
-      <c r="D101">
-        <v>5.751809376288302</v>
-      </c>
-      <c r="E101">
-        <v>13.36132</v>
-      </c>
-      <c r="F101">
-        <v>13.72932</v>
-      </c>
-      <c r="G101">
-        <v>3.67</v>
-      </c>
-      <c r="H101">
-        <v>13.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.94</v>
-      </c>
-      <c r="K101">
-        <v>0.461</v>
-      </c>
-      <c r="L101">
-        <v>1.479</v>
-      </c>
-      <c r="M101">
-        <v>2.756847456</v>
-      </c>
-      <c r="N101">
-        <v>-1.277847456</v>
-      </c>
-      <c r="O101">
-        <v>-0.30668338944</v>
-      </c>
-      <c r="P101">
-        <v>-0.9711640665600001</v>
-      </c>
-      <c r="Q101">
-        <v>-0.51016406656</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.329343971166607</v>
-      </c>
-      <c r="T101">
-        <v>100.2607243253516</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1287557638444831</v>
-      </c>
-      <c r="W101">
-        <v>0.1749458426200278</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5364823493520128</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
